--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -3751,7 +3751,7 @@
         <v>11714</v>
       </c>
       <c r="K64" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="65">
@@ -10921,7 +10921,7 @@
         <v>30689</v>
       </c>
       <c r="K64" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="65">
@@ -21676,7 +21676,7 @@
         <v>1986</v>
       </c>
       <c r="K64" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65">
@@ -28859,7 +28859,7 @@
         <v>5377</v>
       </c>
       <c r="K64" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -3751,7 +3751,7 @@
         <v>11714</v>
       </c>
       <c r="K64" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="65">
@@ -10921,7 +10921,7 @@
         <v>30689</v>
       </c>
       <c r="K64" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="65">
@@ -28859,7 +28859,7 @@
         <v>5377</v>
       </c>
       <c r="K64" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -3733,7 +3733,7 @@
         <v>0.0003662710176611306</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>89429</v>
@@ -7318,7 +7318,7 @@
         <v>0.04932389937106918</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>51126</v>
@@ -10903,7 +10903,7 @@
         <v>0.0136361387130143</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>216983</v>
@@ -10918,10 +10918,10 @@
         <v>0.05847380922845079</v>
       </c>
       <c r="J64" t="n">
-        <v>30689</v>
+        <v>30690</v>
       </c>
       <c r="K64" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="65">
@@ -14488,7 +14488,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -18073,7 +18073,7 @@
         <v>-0.001378347727470994</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>8026</v>
@@ -18091,7 +18091,7 @@
         <v>3695</v>
       </c>
       <c r="K64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65">
@@ -21658,7 +21658,7 @@
         <v>-0.0007605950895981016</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>35152</v>
@@ -25256,7 +25256,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -28841,7 +28841,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>27735</v>
@@ -32426,7 +32426,7 @@
         <v>0.02192767312007515</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>62640</v>
@@ -36011,7 +36011,7 @@
         <v>0.008278113896091423</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>5327</v>
@@ -39596,7 +39596,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -43181,7 +43181,7 @@
         <v>0.07789955604883463</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>19648</v>
@@ -46766,7 +46766,7 @@
         <v>0.07516970469659902</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>18686</v>
@@ -50351,7 +50351,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -3733,7 +3733,7 @@
         <v>0.0003662710176611306</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>89429</v>
@@ -7318,7 +7318,7 @@
         <v>0.04932389937106918</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>51126</v>
@@ -10903,7 +10903,7 @@
         <v>0.0136361387130143</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>216983</v>
@@ -14488,7 +14488,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -18073,7 +18073,7 @@
         <v>-0.001378347727470994</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>8026</v>
@@ -21658,7 +21658,7 @@
         <v>-0.0007605950895981016</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>35152</v>
@@ -25256,7 +25256,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -28841,7 +28841,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>27735</v>
@@ -28859,7 +28859,7 @@
         <v>5377</v>
       </c>
       <c r="K64" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65">
@@ -32426,7 +32426,7 @@
         <v>0.02192767312007515</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>62640</v>
@@ -36011,7 +36011,7 @@
         <v>0.008278113896091423</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>5327</v>
@@ -39596,7 +39596,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -43181,7 +43181,7 @@
         <v>0.07789955604883463</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>19648</v>
@@ -46766,7 +46766,7 @@
         <v>0.07516970469659902</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>18686</v>
@@ -50351,7 +50351,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -46781,7 +46781,7 @@
         <v>1.437935096926207</v>
       </c>
       <c r="J64" t="n">
-        <v>3002</v>
+        <v>3004</v>
       </c>
       <c r="K64" t="n">
         <v>20</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4066,7 +4066,7 @@
         <v>0.001162690798705576</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>89429</v>
@@ -7688,7 +7688,7 @@
         <v>0.04932389937106918</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>51126</v>
@@ -11310,7 +11310,7 @@
         <v>0.01320400972282414</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>216983</v>
@@ -14932,7 +14932,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -18554,7 +18554,7 @@
         <v>-0.001378347727470994</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>8026</v>
@@ -22176,7 +22176,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>35152</v>
@@ -25811,7 +25811,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -29433,7 +29433,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>27735</v>
@@ -33055,7 +33055,7 @@
         <v>0.02192767312007515</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>62640</v>
@@ -36677,7 +36677,7 @@
         <v>0.008278113896091423</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>5327</v>
@@ -40299,7 +40299,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -43921,7 +43921,7 @@
         <v>0.07789955604883463</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>19648</v>
@@ -47543,7 +47543,7 @@
         <v>0.07516970469659902</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>18686</v>
@@ -51165,7 +51165,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4066,7 +4066,7 @@
         <v>0.001162690798705576</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>89429</v>
@@ -7688,7 +7688,7 @@
         <v>0.04932389937106918</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>51126</v>
@@ -11310,7 +11310,7 @@
         <v>0.01320400972282414</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>216983</v>
@@ -14932,7 +14932,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -18554,7 +18554,7 @@
         <v>-0.001378347727470994</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>8026</v>
@@ -22176,7 +22176,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>35152</v>
@@ -25811,7 +25811,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -29433,7 +29433,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>27735</v>
@@ -33055,7 +33055,7 @@
         <v>0.02192767312007515</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>62640</v>
@@ -36677,7 +36677,7 @@
         <v>0.008278113896091423</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>5327</v>
@@ -40299,7 +40299,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -43921,7 +43921,7 @@
         <v>0.07789955604883463</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>19648</v>
@@ -47543,7 +47543,7 @@
         <v>0.07516970469659902</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>18686</v>
@@ -51165,7 +51165,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4084,7 +4084,7 @@
         <v>11714</v>
       </c>
       <c r="K73" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="74">
@@ -11328,7 +11328,7 @@
         <v>30690</v>
       </c>
       <c r="K73" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="74">
@@ -33073,7 +33073,7 @@
         <v>5455</v>
       </c>
       <c r="K73" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4057,13 +4057,13 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>174798</v>
+        <v>174598</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.001162690798705576</v>
+        <v>1.71826226409691e-05</v>
       </c>
       <c r="E73" t="n">
         <v>2</v>
@@ -4084,7 +4084,7 @@
         <v>11714</v>
       </c>
       <c r="K73" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="74">
@@ -4100,7 +4100,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>-0.1304992047963935</v>
+        <v>-0.1295032016403395</v>
       </c>
       <c r="E74" t="n">
         <v>18</v>
@@ -11301,13 +11301,13 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>430174</v>
+        <v>429830</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.01320400972282414</v>
+        <v>0.01239377437772041</v>
       </c>
       <c r="E73" t="n">
         <v>2</v>
@@ -11328,7 +11328,7 @@
         <v>30690</v>
       </c>
       <c r="K73" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="74">
@@ -11344,7 +11344,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>-0.02911380046213858</v>
+        <v>-0.02833678431007608</v>
       </c>
       <c r="E74" t="n">
         <v>18</v>
@@ -33073,7 +33073,7 @@
         <v>5455</v>
       </c>
       <c r="K73" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74">
@@ -36695,7 +36695,7 @@
         <v>5523</v>
       </c>
       <c r="K73" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="74">
@@ -47561,7 +47561,7 @@
         <v>3004</v>
       </c>
       <c r="K73" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4084,7 +4084,7 @@
         <v>11714</v>
       </c>
       <c r="K73" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="74">
@@ -11328,7 +11328,7 @@
         <v>30690</v>
       </c>
       <c r="K73" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="74">
@@ -36695,7 +36695,7 @@
         <v>5523</v>
       </c>
       <c r="K73" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4084,7 +4084,7 @@
         <v>11714</v>
       </c>
       <c r="K73" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4066,7 +4066,7 @@
         <v>1.71826226409691e-05</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>89429</v>
@@ -7688,7 +7688,7 @@
         <v>0.04932389937106918</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>51126</v>
@@ -7706,7 +7706,7 @@
         <v>8183</v>
       </c>
       <c r="K73" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74">
@@ -11301,16 +11301,16 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>429830</v>
+        <v>429841</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.01239377437772041</v>
+        <v>0.01241968306608129</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>216983</v>
@@ -11328,7 +11328,7 @@
         <v>30690</v>
       </c>
       <c r="K73" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="74">
@@ -11344,7 +11344,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>-0.02833678431007608</v>
+        <v>-0.02836165000546714</v>
       </c>
       <c r="E74" t="n">
         <v>18</v>
@@ -14932,7 +14932,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -18554,7 +18554,7 @@
         <v>-0.001378347727470994</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>8026</v>
@@ -22176,7 +22176,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>35152</v>
@@ -25811,7 +25811,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -29433,7 +29433,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>27735</v>
@@ -33055,7 +33055,7 @@
         <v>0.02192767312007515</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>62640</v>
@@ -33073,7 +33073,7 @@
         <v>5455</v>
       </c>
       <c r="K73" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="74">
@@ -36677,7 +36677,7 @@
         <v>0.008278113896091423</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>5327</v>
@@ -36695,7 +36695,7 @@
         <v>5523</v>
       </c>
       <c r="K73" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="74">
@@ -40299,7 +40299,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -43921,7 +43921,7 @@
         <v>0.07789955604883463</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>19648</v>
@@ -47543,7 +47543,7 @@
         <v>0.07516970469659902</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>18686</v>
@@ -51165,7 +51165,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -7706,7 +7706,7 @@
         <v>8183</v>
       </c>
       <c r="K73" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74">
@@ -11328,7 +11328,7 @@
         <v>30690</v>
       </c>
       <c r="K73" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="74">
@@ -33073,7 +33073,7 @@
         <v>5455</v>
       </c>
       <c r="K73" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="74">
@@ -47561,7 +47561,7 @@
         <v>3004</v>
       </c>
       <c r="K73" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -29451,7 +29451,7 @@
         <v>5377</v>
       </c>
       <c r="K73" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="74">
@@ -36695,7 +36695,7 @@
         <v>5523</v>
       </c>
       <c r="K73" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -11325,10 +11325,10 @@
         <v>0.05847380922845079</v>
       </c>
       <c r="J73" t="n">
-        <v>30690</v>
+        <v>30715</v>
       </c>
       <c r="K73" t="n">
-        <v>157</v>
+        <v>138</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4084,7 +4084,7 @@
         <v>11714</v>
       </c>
       <c r="K73" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="74">
@@ -11325,10 +11325,10 @@
         <v>0.05847380922845079</v>
       </c>
       <c r="J73" t="n">
-        <v>30715</v>
+        <v>30794</v>
       </c>
       <c r="K73" t="n">
-        <v>138</v>
+        <v>60</v>
       </c>
     </row>
     <row r="74">
@@ -18572,7 +18572,7 @@
         <v>3695</v>
       </c>
       <c r="K73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="74">
@@ -29448,10 +29448,10 @@
         <v>0.01665765278528935</v>
       </c>
       <c r="J73" t="n">
-        <v>5377</v>
+        <v>5383</v>
       </c>
       <c r="K73" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="74">
@@ -36695,7 +36695,7 @@
         <v>5523</v>
       </c>
       <c r="K73" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4066,7 +4066,7 @@
         <v>1.71826226409691e-05</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>89429</v>
@@ -7688,7 +7688,7 @@
         <v>0.04932389937106918</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>51126</v>
@@ -11310,7 +11310,7 @@
         <v>0.01241968306608129</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>216983</v>
@@ -11328,7 +11328,7 @@
         <v>30794</v>
       </c>
       <c r="K73" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="74">
@@ -14932,7 +14932,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -18554,7 +18554,7 @@
         <v>-0.001378347727470994</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>8026</v>
@@ -22176,7 +22176,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>35152</v>
@@ -25811,7 +25811,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -29433,7 +29433,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>27735</v>
@@ -29451,7 +29451,7 @@
         <v>5383</v>
       </c>
       <c r="K73" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="74">
@@ -33055,7 +33055,7 @@
         <v>0.02192767312007515</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>62640</v>
@@ -36677,7 +36677,7 @@
         <v>0.008278113896091423</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>5327</v>
@@ -40299,7 +40299,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -43921,7 +43921,7 @@
         <v>0.07789955604883463</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>19648</v>
@@ -47543,7 +47543,7 @@
         <v>0.07516970469659902</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>18686</v>
@@ -51165,7 +51165,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4081,10 +4081,10 @@
         <v>0.5962208960681127</v>
       </c>
       <c r="J73" t="n">
-        <v>11714</v>
+        <v>11832</v>
       </c>
       <c r="K73" t="n">
-        <v>115</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -7706,7 +7706,7 @@
         <v>8183</v>
       </c>
       <c r="K73" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="74">
@@ -11328,7 +11328,7 @@
         <v>30794</v>
       </c>
       <c r="K73" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="74">
@@ -29448,10 +29448,10 @@
         <v>0.01665765278528935</v>
       </c>
       <c r="J73" t="n">
-        <v>5383</v>
+        <v>5401</v>
       </c>
       <c r="K73" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -36695,7 +36695,7 @@
         <v>5523</v>
       </c>
       <c r="K73" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4066,7 +4066,7 @@
         <v>1.71826226409691e-05</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>89429</v>
@@ -4084,7 +4084,7 @@
         <v>11832</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -7688,7 +7688,7 @@
         <v>0.04932389937106918</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>51126</v>
@@ -7706,7 +7706,7 @@
         <v>8183</v>
       </c>
       <c r="K73" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="74">
@@ -11301,16 +11301,16 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>429841</v>
+        <v>430309</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.01241968306608129</v>
+        <v>0.01352197998907124</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>216983</v>
@@ -11328,7 +11328,7 @@
         <v>30794</v>
       </c>
       <c r="K73" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="74">
@@ -11344,7 +11344,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>-0.02836165000546714</v>
+        <v>-0.02941839468846805</v>
       </c>
       <c r="E74" t="n">
         <v>18</v>
@@ -14932,7 +14932,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -18554,7 +18554,7 @@
         <v>-0.001378347727470994</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>8026</v>
@@ -22176,7 +22176,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>35152</v>
@@ -22194,7 +22194,7 @@
         <v>1986</v>
       </c>
       <c r="K73" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="74">
@@ -25811,7 +25811,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -29433,7 +29433,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>27735</v>
@@ -33055,7 +33055,7 @@
         <v>0.02192767312007515</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>62640</v>
@@ -36677,7 +36677,7 @@
         <v>0.008278113896091423</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>5327</v>
@@ -36695,7 +36695,7 @@
         <v>5523</v>
       </c>
       <c r="K73" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="74">
@@ -40299,7 +40299,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -43921,7 +43921,7 @@
         <v>0.07789955604883463</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>19648</v>
@@ -43939,7 +43939,7 @@
         <v>784</v>
       </c>
       <c r="K73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -47543,7 +47543,7 @@
         <v>0.07516970469659902</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>18686</v>
@@ -51165,7 +51165,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -51183,7 +51183,7 @@
         <v>424</v>
       </c>
       <c r="K73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -11328,7 +11328,7 @@
         <v>30794</v>
       </c>
       <c r="K73" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="74">
@@ -36695,7 +36695,7 @@
         <v>5523</v>
       </c>
       <c r="K73" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4066,7 +4066,7 @@
         <v>1.71826226409691e-05</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>89429</v>
@@ -4084,7 +4084,7 @@
         <v>11832</v>
       </c>
       <c r="K73" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="74">
@@ -7688,7 +7688,7 @@
         <v>0.04932389937106918</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>51126</v>
@@ -7706,7 +7706,7 @@
         <v>8183</v>
       </c>
       <c r="K73" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="74">
@@ -11310,7 +11310,7 @@
         <v>0.01352197998907124</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>216983</v>
@@ -11328,7 +11328,7 @@
         <v>30794</v>
       </c>
       <c r="K73" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="74">
@@ -14932,7 +14932,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -18554,7 +18554,7 @@
         <v>-0.001378347727470994</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>8026</v>
@@ -18572,7 +18572,7 @@
         <v>3695</v>
       </c>
       <c r="K73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="74">
@@ -22176,7 +22176,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>35152</v>
@@ -25811,7 +25811,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -29433,7 +29433,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>27735</v>
@@ -33055,7 +33055,7 @@
         <v>0.02192767312007515</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>62640</v>
@@ -36677,7 +36677,7 @@
         <v>0.008278113896091423</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>5327</v>
@@ -40299,7 +40299,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -43921,7 +43921,7 @@
         <v>0.07789955604883463</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>19648</v>
@@ -47543,7 +47543,7 @@
         <v>0.07516970469659902</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>18686</v>
@@ -51165,7 +51165,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4066,7 +4066,7 @@
         <v>1.71826226409691e-05</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>89429</v>
@@ -4084,7 +4084,7 @@
         <v>11832</v>
       </c>
       <c r="K73" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="74">
@@ -7688,7 +7688,7 @@
         <v>0.04932389937106918</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>51126</v>
@@ -11310,7 +11310,7 @@
         <v>0.01352197998907124</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>216983</v>
@@ -11328,7 +11328,7 @@
         <v>30794</v>
       </c>
       <c r="K73" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="74">
@@ -14932,7 +14932,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -18554,7 +18554,7 @@
         <v>-0.001378347727470994</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>8026</v>
@@ -22176,7 +22176,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>35152</v>
@@ -25811,7 +25811,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -29433,7 +29433,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>27735</v>
@@ -33046,16 +33046,16 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>97916</v>
+        <v>97909</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.02192767312007515</v>
+        <v>0.0218546156656056</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>62640</v>
@@ -33089,7 +33089,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>-0.09212998897013767</v>
+        <v>-0.09206508084037218</v>
       </c>
       <c r="E74" t="n">
         <v>18</v>
@@ -36677,7 +36677,7 @@
         <v>0.008278113896091423</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>5327</v>
@@ -36695,7 +36695,7 @@
         <v>5523</v>
       </c>
       <c r="K73" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="74">
@@ -40299,7 +40299,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -43921,7 +43921,7 @@
         <v>0.07789955604883463</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>19648</v>
@@ -47543,7 +47543,7 @@
         <v>0.07516970469659902</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>18686</v>
@@ -51165,7 +51165,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4084,7 +4084,7 @@
         <v>11832</v>
       </c>
       <c r="K73" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74">
@@ -36695,7 +36695,7 @@
         <v>5523</v>
       </c>
       <c r="K73" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4066,25 +4066,25 @@
         <v>1.71826226409691e-05</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
-        <v>89429</v>
+        <v>90046</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>32808</v>
+        <v>42297</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.5962208960681127</v>
+        <v>0.7281891902479792</v>
       </c>
       <c r="J73" t="n">
-        <v>11832</v>
+        <v>11849</v>
       </c>
       <c r="K73" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4115,7 +4115,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>-0.7037885419308393</v>
+        <v>-0.7264078946374194</v>
       </c>
       <c r="J74" t="n">
         <v>6053</v>
@@ -7688,7 +7688,7 @@
         <v>0.04932389937106918</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>51126</v>
@@ -11301,16 +11301,16 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>430309</v>
+        <v>430396</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.01352197998907124</v>
+        <v>0.01372689416065271</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>216983</v>
@@ -11319,16 +11319,16 @@
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>13397</v>
+        <v>19079</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.05847380922845079</v>
+        <v>0.08457958309786678</v>
       </c>
       <c r="J73" t="n">
         <v>30794</v>
       </c>
       <c r="K73" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="74">
@@ -11344,7 +11344,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>-0.02941839468846805</v>
+        <v>-0.02961458749616632</v>
       </c>
       <c r="E74" t="n">
         <v>18</v>
@@ -11359,7 +11359,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>-0.5784095841652921</v>
+        <v>-0.5885572434360464</v>
       </c>
       <c r="J74" t="n">
         <v>20283</v>
@@ -14932,7 +14932,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -18554,7 +18554,7 @@
         <v>-0.001378347727470994</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>8026</v>
@@ -22176,7 +22176,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>35152</v>
@@ -25811,7 +25811,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -29433,7 +29433,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>27735</v>
@@ -33055,7 +33055,7 @@
         <v>0.0218546156656056</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>62640</v>
@@ -36677,7 +36677,7 @@
         <v>0.008278113896091423</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>5327</v>
@@ -36692,10 +36692,10 @@
         <v>33.48673785738891</v>
       </c>
       <c r="J73" t="n">
-        <v>5523</v>
+        <v>5585</v>
       </c>
       <c r="K73" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -40299,7 +40299,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -43921,7 +43921,7 @@
         <v>0.07789955604883463</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>19648</v>
@@ -43936,10 +43936,10 @@
         <v>0.1193191393741925</v>
       </c>
       <c r="J73" t="n">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="K73" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -47543,7 +47543,7 @@
         <v>0.07516970469659902</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>18686</v>
@@ -47558,10 +47558,10 @@
         <v>1.437935096926207</v>
       </c>
       <c r="J73" t="n">
-        <v>3004</v>
+        <v>3025</v>
       </c>
       <c r="K73" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -51165,7 +51165,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -51180,10 +51180,10 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="K73" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4066,7 +4066,7 @@
         <v>1.71826226409691e-05</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>90046</v>
@@ -7688,7 +7688,7 @@
         <v>0.04932389937106918</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>51126</v>
@@ -7703,10 +7703,10 @@
         <v>-0.001172195522213105</v>
       </c>
       <c r="J73" t="n">
-        <v>8183</v>
+        <v>8222</v>
       </c>
       <c r="K73" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -11310,7 +11310,7 @@
         <v>0.01372689416065271</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>216983</v>
@@ -14932,7 +14932,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -18554,7 +18554,7 @@
         <v>-0.001378347727470994</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>8026</v>
@@ -22176,7 +22176,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>35152</v>
@@ -25811,7 +25811,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -29433,7 +29433,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>27735</v>
@@ -33055,7 +33055,7 @@
         <v>0.0218546156656056</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>62640</v>
@@ -36677,7 +36677,7 @@
         <v>0.008278113896091423</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>5327</v>
@@ -40299,7 +40299,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -43921,7 +43921,7 @@
         <v>0.07789955604883463</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>19648</v>
@@ -47543,7 +47543,7 @@
         <v>0.07516970469659902</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>18686</v>
@@ -51165,7 +51165,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -11301,13 +11301,13 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>430396</v>
+        <v>430394</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.01372689416065271</v>
+        <v>0.01372218349004164</v>
       </c>
       <c r="E73" t="n">
         <v>11</v>
@@ -11325,10 +11325,10 @@
         <v>0.08457958309786678</v>
       </c>
       <c r="J73" t="n">
-        <v>30794</v>
+        <v>30871</v>
       </c>
       <c r="K73" t="n">
-        <v>78</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -11344,7 +11344,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>-0.02961458749616632</v>
+        <v>-0.02961007820740996</v>
       </c>
       <c r="E74" t="n">
         <v>18</v>
@@ -18569,10 +18569,10 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>3695</v>
+        <v>3706</v>
       </c>
       <c r="K73" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -22191,10 +22191,10 @@
         <v>-0.009985734664764621</v>
       </c>
       <c r="J73" t="n">
-        <v>1986</v>
+        <v>2006</v>
       </c>
       <c r="K73" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -33070,10 +33070,10 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>5455</v>
+        <v>5484</v>
       </c>
       <c r="K73" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4066,7 +4066,7 @@
         <v>1.71826226409691e-05</v>
       </c>
       <c r="E73" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F73" t="n">
         <v>90046</v>
@@ -7688,7 +7688,7 @@
         <v>0.04932389937106918</v>
       </c>
       <c r="E73" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F73" t="n">
         <v>51126</v>
@@ -11310,7 +11310,7 @@
         <v>0.01372218349004164</v>
       </c>
       <c r="E73" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F73" t="n">
         <v>216983</v>
@@ -14932,7 +14932,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -18545,16 +18545,16 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>57236</v>
+        <v>57338</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>-0.001378347727470994</v>
+        <v>0.0004012911105295298</v>
       </c>
       <c r="E73" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F73" t="n">
         <v>8026</v>
@@ -18588,7 +18588,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>-0.0231148228387728</v>
+        <v>-0.02485262827444278</v>
       </c>
       <c r="E74" t="n">
         <v>18</v>
@@ -22176,7 +22176,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F73" t="n">
         <v>35152</v>
@@ -25811,7 +25811,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -29433,7 +29433,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E73" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F73" t="n">
         <v>27735</v>
@@ -33055,7 +33055,7 @@
         <v>0.0218546156656056</v>
       </c>
       <c r="E73" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F73" t="n">
         <v>62640</v>
@@ -36677,7 +36677,7 @@
         <v>0.008278113896091423</v>
       </c>
       <c r="E73" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F73" t="n">
         <v>5327</v>
@@ -40299,7 +40299,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E73" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -43921,7 +43921,7 @@
         <v>0.07789955604883463</v>
       </c>
       <c r="E73" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F73" t="n">
         <v>19648</v>
@@ -47543,7 +47543,7 @@
         <v>0.07516970469659902</v>
       </c>
       <c r="E73" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F73" t="n">
         <v>18686</v>
@@ -51165,7 +51165,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -1350,7 +1350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4066,7 +4066,7 @@
         <v>1.71826226409691e-05</v>
       </c>
       <c r="E73" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F73" t="n">
         <v>90046</v>
@@ -4386,60 +4386,60 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>151987</v>
+        <v>174598</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.1294882442223431</v>
+        <v>1.71826226409691e-05</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>36208</v>
+        <v>90046</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>42297</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.5271810809752021</v>
+        <v>0.7281891902479792</v>
       </c>
       <c r="J82" t="n">
-        <v>6022</v>
+        <v>11849</v>
       </c>
       <c r="K82" t="n">
-        <v>3510</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>151737</v>
+        <v>151987</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>-0.001644877522419681</v>
+        <v>-0.1295032016403395</v>
       </c>
       <c r="E83" t="n">
         <v>7</v>
       </c>
       <c r="F83" t="n">
-        <v>37410</v>
+        <v>36208</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -4448,13 +4448,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.03319708351745471</v>
+        <v>-0.7264078946374194</v>
       </c>
       <c r="J83" t="n">
-        <v>9487</v>
+        <v>6022</v>
       </c>
       <c r="K83" t="n">
-        <v>120</v>
+        <v>3510</v>
       </c>
     </row>
     <row r="84">
@@ -4470,7 +4470,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>-0.001644877522419681</v>
       </c>
       <c r="E84" t="n">
         <v>7</v>
@@ -4485,7 +4485,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>0.03319708351745471</v>
       </c>
       <c r="J84" t="n">
         <v>9487</v>
@@ -4497,7 +4497,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4510,7 +4510,7 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F85" t="n">
         <v>37410</v>
@@ -4528,29 +4528,29 @@
         <v>9487</v>
       </c>
       <c r="K85" t="n">
-        <v>461</v>
+        <v>120</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>160193</v>
+        <v>151737</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.05572800305792259</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F86" t="n">
-        <v>37411</v>
+        <v>37410</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -4559,35 +4559,35 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>2.673082063619353e-05</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>10345</v>
+        <v>9487</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>461</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>160051</v>
+        <v>160193</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>-0.0008864307429163571</v>
+        <v>0.05572800305792259</v>
       </c>
       <c r="E87" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F87" t="n">
-        <v>61855</v>
+        <v>37411</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -4596,10 +4596,10 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.6533907139611345</v>
+        <v>2.673082063619353e-05</v>
       </c>
       <c r="J87" t="n">
-        <v>10652</v>
+        <v>10345</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -4608,23 +4608,23 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>169812</v>
+        <v>160051</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.06098681045416773</v>
+        <v>-0.0008864307429163571</v>
       </c>
       <c r="E88" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F88" t="n">
-        <v>71833</v>
+        <v>61855</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -4633,10 +4633,10 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.1613127475547652</v>
+        <v>0.6533907139611345</v>
       </c>
       <c r="J88" t="n">
-        <v>11057</v>
+        <v>10652</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -4645,97 +4645,97 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>174595</v>
+        <v>169812</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.028166442889784</v>
+        <v>0.06098681045416773</v>
       </c>
       <c r="E89" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F89" t="n">
-        <v>73935</v>
+        <v>71833</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>25005</v>
+        <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.377361379867192</v>
+        <v>0.1613127475547652</v>
       </c>
       <c r="J89" t="n">
-        <v>11486</v>
+        <v>11057</v>
       </c>
       <c r="K89" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>151987</v>
+        <v>174595</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.1294882442223431</v>
+        <v>0.028166442889784</v>
       </c>
       <c r="E90" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F90" t="n">
-        <v>36208</v>
+        <v>73935</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>25005</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.6340408328279765</v>
+        <v>0.377361379867192</v>
       </c>
       <c r="J90" t="n">
-        <v>6022</v>
+        <v>11486</v>
       </c>
       <c r="K90" t="n">
-        <v>3510</v>
+        <v>92</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>151737</v>
+        <v>151987</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>-0.001644877522419681</v>
+        <v>-0.1294882442223431</v>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F91" t="n">
-        <v>37410</v>
+        <v>36208</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -4744,19 +4744,19 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.03319708351745471</v>
+        <v>-0.6340408328279765</v>
       </c>
       <c r="J91" t="n">
-        <v>9487</v>
+        <v>6022</v>
       </c>
       <c r="K91" t="n">
-        <v>173</v>
+        <v>3510</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -4766,10 +4766,10 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>-0.001644877522419681</v>
       </c>
       <c r="E92" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F92" t="n">
         <v>37410</v>
@@ -4781,35 +4781,35 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.03319708351745471</v>
       </c>
       <c r="J92" t="n">
         <v>9487</v>
       </c>
       <c r="K92" t="n">
-        <v>504</v>
+        <v>173</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>160193</v>
+        <v>151737</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.05572800305792259</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F93" t="n">
-        <v>37411</v>
+        <v>37410</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -4818,35 +4818,35 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>2.673082063619353e-05</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>10345</v>
+        <v>9487</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>159626</v>
+        <v>160193</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>-0.003539480501644891</v>
+        <v>0.05572800305792259</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F94" t="n">
-        <v>61855</v>
+        <v>37411</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -4855,35 +4855,35 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0.6533907139611345</v>
+        <v>2.673082063619353e-05</v>
       </c>
       <c r="J94" t="n">
-        <v>10672</v>
+        <v>10345</v>
       </c>
       <c r="K94" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>169812</v>
+        <v>159626</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.06381165975467655</v>
+        <v>-0.003539480501644891</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F95" t="n">
-        <v>76579</v>
+        <v>61855</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -4892,71 +4892,108 @@
         <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0.2380405787729367</v>
+        <v>0.6533907139611345</v>
       </c>
       <c r="J95" t="n">
-        <v>11080</v>
+        <v>10672</v>
       </c>
       <c r="K95" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>174750</v>
+        <v>169812</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>0.02907921701646527</v>
+        <v>0.06381165975467655</v>
       </c>
       <c r="E96" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F96" t="n">
-        <v>73935</v>
+        <v>76579</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>25005</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>0.2919991120281017</v>
+        <v>0.2380405787729367</v>
       </c>
       <c r="J96" t="n">
-        <v>11597</v>
+        <v>11080</v>
       </c>
       <c r="K96" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>174750</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0.02907921701646527</v>
+      </c>
+      <c r="E97" t="n">
+        <v>10</v>
+      </c>
+      <c r="F97" t="n">
+        <v>73935</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>25005</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>0.2919991120281017</v>
+      </c>
+      <c r="J97" t="n">
+        <v>11597</v>
+      </c>
+      <c r="K97" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>22763</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>37727</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
         <v>25005</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>5575</v>
       </c>
     </row>
@@ -4972,7 +5009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7688,7 +7725,7 @@
         <v>0.04932389937106918</v>
       </c>
       <c r="E73" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F73" t="n">
         <v>51126</v>
@@ -8008,23 +8045,23 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>116617</v>
+        <v>133474</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.09908608422239905</v>
+        <v>0.03114112002966557</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>51126</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -8033,29 +8070,29 @@
         <v>0</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-1</v>
+        <v>-0.001172195522213105</v>
       </c>
       <c r="J82" t="n">
-        <v>4900</v>
+        <v>8222</v>
       </c>
       <c r="K82" t="n">
-        <v>1975</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>116931</v>
+        <v>116617</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.00269257483900289</v>
+        <v>-0.1262942595561682</v>
       </c>
       <c r="E83" t="n">
         <v>7</v>
@@ -8070,13 +8107,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J83" t="n">
-        <v>5754</v>
+        <v>4900</v>
       </c>
       <c r="K83" t="n">
-        <v>1633</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="84">
@@ -8092,7 +8129,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.00269257483900289</v>
       </c>
       <c r="E84" t="n">
         <v>7</v>
@@ -8119,20 +8156,20 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>116775</v>
+        <v>116931</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>-0.001334120122123303</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -8150,26 +8187,26 @@
         <v>5754</v>
       </c>
       <c r="K85" t="n">
-        <v>1767</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>118544</v>
+        <v>116775</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.01514879040890602</v>
+        <v>-0.001334120122123303</v>
       </c>
       <c r="E86" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -8184,29 +8221,29 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>7368</v>
+        <v>5754</v>
       </c>
       <c r="K86" t="n">
-        <v>45</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>116769</v>
+        <v>118544</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>-0.01497334323120529</v>
+        <v>0.01514879040890602</v>
       </c>
       <c r="E87" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -8221,32 +8258,32 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>7619</v>
+        <v>7368</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>119570</v>
+        <v>116769</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.02398753093714941</v>
+        <v>-0.01497334323120529</v>
       </c>
       <c r="E88" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F88" t="n">
-        <v>51186</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -8258,7 +8295,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>7864</v>
+        <v>7619</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -8267,20 +8304,20 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>129443</v>
+        <v>119570</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.0825708789830225</v>
+        <v>0.02398753093714941</v>
       </c>
       <c r="E89" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F89" t="n">
         <v>51186</v>
@@ -8295,32 +8332,32 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>7981</v>
+        <v>7864</v>
       </c>
       <c r="K89" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>116617</v>
+        <v>129443</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.09908608422239905</v>
+        <v>0.0825708789830225</v>
       </c>
       <c r="E90" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>51186</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -8329,32 +8366,32 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>4900</v>
+        <v>7981</v>
       </c>
       <c r="K90" t="n">
-        <v>1975</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>116931</v>
+        <v>116617</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.00269257483900289</v>
+        <v>-0.09908608422239905</v>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -8366,32 +8403,32 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J91" t="n">
-        <v>5754</v>
+        <v>4900</v>
       </c>
       <c r="K91" t="n">
-        <v>1644</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>116775</v>
+        <v>116931</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>-0.001334120122123303</v>
+        <v>0.00269257483900289</v>
       </c>
       <c r="E92" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -8409,26 +8446,26 @@
         <v>5754</v>
       </c>
       <c r="K92" t="n">
-        <v>1779</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>118544</v>
+        <v>116775</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.01514879040890602</v>
+        <v>-0.001334120122123303</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -8443,29 +8480,29 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>7368</v>
+        <v>5754</v>
       </c>
       <c r="K93" t="n">
-        <v>45</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>117052</v>
+        <v>118544</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>-0.01258604400053988</v>
+        <v>0.01514879040890602</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -8480,32 +8517,32 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>7631</v>
+        <v>7368</v>
       </c>
       <c r="K94" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>120729</v>
+        <v>117052</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.03141338892116324</v>
+        <v>-0.01258604400053988</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F95" t="n">
-        <v>51186</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -8517,29 +8554,29 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>7860</v>
+        <v>7631</v>
       </c>
       <c r="K95" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>130408</v>
+        <v>120729</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>0.08017129272999859</v>
+        <v>0.03141338892116324</v>
       </c>
       <c r="E96" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F96" t="n">
         <v>51186</v>
@@ -8554,31 +8591,68 @@
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>7997</v>
+        <v>7860</v>
       </c>
       <c r="K96" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>130408</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0.08017129272999859</v>
+      </c>
+      <c r="E97" t="n">
+        <v>10</v>
+      </c>
+      <c r="F97" t="n">
+        <v>51186</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>7997</v>
+      </c>
+      <c r="K97" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>13791</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>51186</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="4" t="n">
         <v>3097</v>
       </c>
     </row>
@@ -8594,7 +8668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -11310,7 +11384,7 @@
         <v>0.01372218349004164</v>
       </c>
       <c r="E73" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F73" t="n">
         <v>216983</v>
@@ -11630,60 +11704,60 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>417637</v>
+        <v>430394</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.01637811446780549</v>
+        <v>0.0136672703849116</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>106761</v>
+        <v>216983</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>19079</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.5094898760871662</v>
+        <v>0.08457958309786678</v>
       </c>
       <c r="J82" t="n">
-        <v>26884</v>
+        <v>30871</v>
       </c>
       <c r="K82" t="n">
-        <v>2238</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>417941</v>
+        <v>417637</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.0007279048551732725</v>
+        <v>-0.02964028308944827</v>
       </c>
       <c r="E83" t="n">
         <v>7</v>
       </c>
       <c r="F83" t="n">
-        <v>128132</v>
+        <v>106761</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -11692,13 +11766,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.2001760942666329</v>
+        <v>-0.5477416949784378</v>
       </c>
       <c r="J83" t="n">
-        <v>28891</v>
+        <v>26884</v>
       </c>
       <c r="K83" t="n">
-        <v>44</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="84">
@@ -11714,7 +11788,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.0007279048551732725</v>
       </c>
       <c r="E84" t="n">
         <v>7</v>
@@ -11729,7 +11803,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>0.2001760942666329</v>
       </c>
       <c r="J84" t="n">
         <v>28891</v>
@@ -11741,23 +11815,23 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>418037</v>
+        <v>417941</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.0002296974931868374</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F85" t="n">
-        <v>142432</v>
+        <v>128132</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -11766,35 +11840,35 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.1116036587269379</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>28876</v>
+        <v>28891</v>
       </c>
       <c r="K85" t="n">
-        <v>463</v>
+        <v>44</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>423120</v>
+        <v>418037</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.01215921078756187</v>
+        <v>0.0002296974931868374</v>
       </c>
       <c r="E86" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F86" t="n">
-        <v>143945</v>
+        <v>142432</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -11803,35 +11877,35 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.01062261289597843</v>
+        <v>0.1116036587269379</v>
       </c>
       <c r="J86" t="n">
-        <v>28900</v>
+        <v>28876</v>
       </c>
       <c r="K86" t="n">
-        <v>621</v>
+        <v>463</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>422876</v>
+        <v>423120</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>-0.0005766685573832483</v>
+        <v>0.01215921078756187</v>
       </c>
       <c r="E87" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F87" t="n">
-        <v>176028</v>
+        <v>143945</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -11840,35 +11914,35 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.2228837403174824</v>
+        <v>0.01062261289597843</v>
       </c>
       <c r="J87" t="n">
-        <v>29820</v>
+        <v>28900</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>621</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>423508</v>
+        <v>422876</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.0014945279467267</v>
+        <v>-0.0005766685573832483</v>
       </c>
       <c r="E88" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F88" t="n">
-        <v>216739</v>
+        <v>176028</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -11877,109 +11951,109 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.2312757061376599</v>
+        <v>0.2228837403174824</v>
       </c>
       <c r="J88" t="n">
-        <v>30128</v>
+        <v>29820</v>
       </c>
       <c r="K88" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>424570</v>
+        <v>423508</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.002507626774464709</v>
+        <v>0.0014945279467267</v>
       </c>
       <c r="E89" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F89" t="n">
-        <v>216828</v>
+        <v>216739</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>10880</v>
+        <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.05060925813997481</v>
+        <v>0.2312757061376599</v>
       </c>
       <c r="J89" t="n">
-        <v>30496</v>
+        <v>30128</v>
       </c>
       <c r="K89" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>417637</v>
+        <v>424570</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.01632946275054761</v>
+        <v>0.002507626774464709</v>
       </c>
       <c r="E90" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F90" t="n">
-        <v>106761</v>
+        <v>216828</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>10880</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.5311495423964024</v>
+        <v>0.05060925813997481</v>
       </c>
       <c r="J90" t="n">
-        <v>26884</v>
+        <v>30496</v>
       </c>
       <c r="K90" t="n">
-        <v>2238</v>
+        <v>36</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>417941</v>
+        <v>417637</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.0007279048551732725</v>
+        <v>-0.01632946275054761</v>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F91" t="n">
-        <v>37689</v>
+        <v>106761</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -11988,35 +12062,35 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>-0.6469778289824936</v>
+        <v>-0.5311495423964024</v>
       </c>
       <c r="J91" t="n">
-        <v>28888</v>
+        <v>26884</v>
       </c>
       <c r="K91" t="n">
-        <v>180</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>418037</v>
+        <v>417941</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.0002296974931868374</v>
+        <v>0.0007279048551732725</v>
       </c>
       <c r="E92" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F92" t="n">
-        <v>142432</v>
+        <v>37689</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -12025,35 +12099,35 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>2.779139802064263</v>
+        <v>-0.6469778289824936</v>
       </c>
       <c r="J92" t="n">
-        <v>28876</v>
+        <v>28888</v>
       </c>
       <c r="K92" t="n">
-        <v>488</v>
+        <v>180</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>423590</v>
+        <v>418037</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.01328351318184754</v>
+        <v>0.0002296974931868374</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F93" t="n">
-        <v>143945</v>
+        <v>142432</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -12062,35 +12136,35 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.01062261289597843</v>
+        <v>2.779139802064263</v>
       </c>
       <c r="J93" t="n">
-        <v>28900</v>
+        <v>28876</v>
       </c>
       <c r="K93" t="n">
-        <v>621</v>
+        <v>488</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>423173</v>
+        <v>423590</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>-0.000984442503364102</v>
+        <v>0.01328351318184754</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F94" t="n">
-        <v>180505</v>
+        <v>143945</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -12099,35 +12173,35 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0.2539858973913647</v>
+        <v>0.01062261289597843</v>
       </c>
       <c r="J94" t="n">
-        <v>29830</v>
+        <v>28900</v>
       </c>
       <c r="K94" t="n">
-        <v>8</v>
+        <v>621</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>423508</v>
+        <v>423173</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.0007916384079324531</v>
+        <v>-0.000984442503364102</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F95" t="n">
-        <v>216739</v>
+        <v>180505</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -12136,71 +12210,108 @@
         <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0.2007368216946899</v>
+        <v>0.2539858973913647</v>
       </c>
       <c r="J95" t="n">
-        <v>30134</v>
+        <v>29830</v>
       </c>
       <c r="K95" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>423508</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.0007916384079324531</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="n">
+        <v>216739</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0.2007368216946899</v>
+      </c>
+      <c r="J96" t="n">
+        <v>30134</v>
+      </c>
+      <c r="K96" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B97" t="n">
         <v>424570</v>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="n">
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
         <v>0.002507626774464709</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>10</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F97" t="n">
         <v>216828</v>
       </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
         <v>10880</v>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I97" s="3" t="n">
         <v>0.05060925813997481</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>30551</v>
       </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>6933</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>110067</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
         <v>10880</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>3630</v>
       </c>
     </row>
@@ -12216,7 +12327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -14932,7 +15043,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -15252,20 +15363,20 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>7262</v>
+        <v>9514</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.2367038049190666</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -15280,26 +15391,26 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>218</v>
+        <v>1714</v>
       </c>
       <c r="K82" t="n">
-        <v>1473</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>8178</v>
+        <v>7262</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.1261360506747453</v>
+        <v>-0.2367038049190666</v>
       </c>
       <c r="E83" t="n">
         <v>7</v>
@@ -15317,10 +15428,10 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="K83" t="n">
-        <v>1479</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="84">
@@ -15336,7 +15447,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.1261360506747453</v>
       </c>
       <c r="E84" t="n">
         <v>7</v>
@@ -15363,7 +15474,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -15376,7 +15487,7 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -15394,26 +15505,26 @@
         <v>180</v>
       </c>
       <c r="K85" t="n">
-        <v>1497</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>8223</v>
+        <v>8178</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.005502567865003668</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -15431,26 +15542,26 @@
         <v>180</v>
       </c>
       <c r="K86" t="n">
-        <v>1502</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>8333</v>
+        <v>8223</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.01337711297579959</v>
+        <v>0.005502567865003668</v>
       </c>
       <c r="E87" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -15465,29 +15576,29 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>1693</v>
+        <v>180</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>9525</v>
+        <v>8333</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.1430457218288732</v>
+        <v>0.01337711297579959</v>
       </c>
       <c r="E88" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -15502,29 +15613,29 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>1701</v>
+        <v>1693</v>
       </c>
       <c r="K88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>9514</v>
+        <v>9525</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>-0.001154855643044619</v>
+        <v>0.1430457218288732</v>
       </c>
       <c r="E89" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -15539,29 +15650,29 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>1703</v>
+        <v>1701</v>
       </c>
       <c r="K89" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>7262</v>
+        <v>9514</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.2367038049190666</v>
+        <v>-0.001154855643044619</v>
       </c>
       <c r="E90" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -15576,29 +15687,29 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>218</v>
+        <v>1703</v>
       </c>
       <c r="K90" t="n">
-        <v>1473</v>
+        <v>10</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>8178</v>
+        <v>7262</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.1261360506747453</v>
+        <v>-0.2367038049190666</v>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -15613,16 +15724,16 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="K91" t="n">
-        <v>1482</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -15632,10 +15743,10 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.1261360506747453</v>
       </c>
       <c r="E92" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -15653,26 +15764,26 @@
         <v>180</v>
       </c>
       <c r="K92" t="n">
-        <v>1498</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>8223</v>
+        <v>8178</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.005502567865003668</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -15690,26 +15801,26 @@
         <v>180</v>
       </c>
       <c r="K93" t="n">
-        <v>1502</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>8333</v>
+        <v>8223</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.01337711297579959</v>
+        <v>0.005502567865003668</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -15724,105 +15835,142 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>1693</v>
+        <v>180</v>
       </c>
       <c r="K94" t="n">
-        <v>1</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>9525</v>
+        <v>8333</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.1430457218288732</v>
+        <v>0.01337711297579959</v>
       </c>
       <c r="E95" t="n">
+        <v>4</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>1693</v>
+      </c>
+      <c r="K95" t="n">
         <v>1</v>
-      </c>
-      <c r="F95" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" t="n">
-        <v>1703</v>
-      </c>
-      <c r="K95" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>9525</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.1430457218288732</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>1703</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B97" t="n">
         <v>9514</v>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="n">
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
         <v>-0.001154855643044619</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>10</v>
       </c>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" t="n">
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
         <v>1713</v>
       </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>2252</v>
       </c>
-      <c r="F97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="4" t="n">
+      <c r="F98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="4" t="n">
         <v>1532</v>
       </c>
     </row>
@@ -15838,7 +15986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -18554,7 +18702,7 @@
         <v>0.0004012911105295298</v>
       </c>
       <c r="E73" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F73" t="n">
         <v>8026</v>
@@ -18874,60 +19022,60 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>55913</v>
+        <v>57338</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.02446131030271308</v>
+        <v>0.0004012911105295298</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>1959</v>
+        <v>8026</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>62319</v>
       </c>
       <c r="I82" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>643</v>
+        <v>3706</v>
       </c>
       <c r="K82" t="n">
-        <v>2718</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>57113</v>
+        <v>55913</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.02146191404503425</v>
+        <v>-0.02485262827444278</v>
       </c>
       <c r="E83" t="n">
         <v>7</v>
       </c>
       <c r="F83" t="n">
-        <v>1956</v>
+        <v>1959</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -18936,13 +19084,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>-0.001531393568147014</v>
+        <v>-0.9721515388442675</v>
       </c>
       <c r="J83" t="n">
         <v>643</v>
       </c>
       <c r="K83" t="n">
-        <v>2860</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="84">
@@ -18958,7 +19106,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.02146191404503425</v>
       </c>
       <c r="E84" t="n">
         <v>7</v>
@@ -18973,7 +19121,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>-0.001531393568147014</v>
       </c>
       <c r="J84" t="n">
         <v>643</v>
@@ -18985,20 +19133,20 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>57117</v>
+        <v>57113</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>7.003659412042792e-05</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F85" t="n">
         <v>1956</v>
@@ -19013,16 +19161,16 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>3494</v>
+        <v>643</v>
       </c>
       <c r="K85" t="n">
-        <v>67</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -19032,10 +19180,10 @@
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0</v>
+        <v>7.003659412042792e-05</v>
       </c>
       <c r="E86" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F86" t="n">
         <v>1956</v>
@@ -19053,26 +19201,26 @@
         <v>3494</v>
       </c>
       <c r="K86" t="n">
-        <v>88</v>
+        <v>67</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>57138</v>
+        <v>57117</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.000367666369031987</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F87" t="n">
         <v>1956</v>
@@ -19087,29 +19235,29 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>3667</v>
+        <v>3494</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>57236</v>
+        <v>57138</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.001715145787391928</v>
+        <v>0.000367666369031987</v>
       </c>
       <c r="E88" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F88" t="n">
         <v>1956</v>
@@ -19124,106 +19272,106 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>3673</v>
+        <v>3667</v>
       </c>
       <c r="K88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>57315</v>
+        <v>57236</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.001380250192186736</v>
+        <v>0.001715145787391928</v>
       </c>
       <c r="E89" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>1956</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>6504</v>
+        <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>2.325153374233129</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>3679</v>
+        <v>3673</v>
       </c>
       <c r="K89" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>55913</v>
+        <v>57315</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.02446131030271308</v>
+        <v>0.001380250192186736</v>
       </c>
       <c r="E90" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F90" t="n">
-        <v>1959</v>
+        <v>0</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>6504</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.6988007380073801</v>
+        <v>2.325153374233129</v>
       </c>
       <c r="J90" t="n">
-        <v>643</v>
+        <v>3679</v>
       </c>
       <c r="K90" t="n">
-        <v>2718</v>
+        <v>13</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>57113</v>
+        <v>55913</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.02146191404503425</v>
+        <v>-0.02446131030271308</v>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F91" t="n">
-        <v>1956</v>
+        <v>1959</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -19232,32 +19380,32 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>-0.001531393568147014</v>
+        <v>-0.6988007380073801</v>
       </c>
       <c r="J91" t="n">
         <v>643</v>
       </c>
       <c r="K91" t="n">
-        <v>2863</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>57117</v>
+        <v>57113</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>7.003659412042792e-05</v>
+        <v>0.02146191404503425</v>
       </c>
       <c r="E92" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F92" t="n">
         <v>1956</v>
@@ -19269,32 +19417,32 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>-0.001531393568147014</v>
       </c>
       <c r="J92" t="n">
-        <v>3494</v>
+        <v>643</v>
       </c>
       <c r="K92" t="n">
-        <v>68</v>
+        <v>2863</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>57242</v>
+        <v>57117</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.002188490291857065</v>
+        <v>7.003659412042792e-05</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F93" t="n">
         <v>1956</v>
@@ -19312,26 +19460,26 @@
         <v>3494</v>
       </c>
       <c r="K93" t="n">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>57236</v>
+        <v>57242</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>-0.0001048181405261871</v>
+        <v>0.002188490291857065</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F94" t="n">
         <v>1956</v>
@@ -19346,29 +19494,29 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>3672</v>
+        <v>3494</v>
       </c>
       <c r="K94" t="n">
-        <v>1</v>
+        <v>88</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>57315</v>
+        <v>57236</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.001380250192186736</v>
+        <v>-0.0001048181405261871</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F95" t="n">
         <v>1956</v>
@@ -19383,7 +19531,7 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>3673</v>
+        <v>3672</v>
       </c>
       <c r="K95" t="n">
         <v>1</v>
@@ -19392,7 +19540,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -19402,49 +19550,86 @@
         <v>0</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>0</v>
+        <v>0.001380250192186736</v>
       </c>
       <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1956</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>3673</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>57315</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
         <v>10</v>
       </c>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
         <v>6504</v>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I97" s="3" t="n">
         <v>2.325153374233129</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>3679</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K97" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>1402</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>-1959</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
         <v>6504</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>3036</v>
       </c>
     </row>
@@ -19460,7 +19645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -22176,7 +22361,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F73" t="n">
         <v>35152</v>
@@ -22496,60 +22681,60 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>30704</v>
+        <v>32844</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.06515649738156132</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>32196</v>
+        <v>35152</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>936</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.116756282234171</v>
+        <v>-0.009985734664764621</v>
       </c>
       <c r="J82" t="n">
-        <v>335</v>
+        <v>2006</v>
       </c>
       <c r="K82" t="n">
-        <v>1538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>30931</v>
+        <v>30704</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.007393173527879104</v>
+        <v>-0.06515649738156132</v>
       </c>
       <c r="E83" t="n">
         <v>7</v>
       </c>
       <c r="F83" t="n">
-        <v>35515</v>
+        <v>32196</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -22558,13 +22743,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.1030873400422413</v>
+        <v>-0.1078474839281756</v>
       </c>
       <c r="J83" t="n">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K83" t="n">
-        <v>1546</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="84">
@@ -22580,7 +22765,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.007393173527879104</v>
       </c>
       <c r="E84" t="n">
         <v>7</v>
@@ -22595,7 +22780,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>0.1030873400422413</v>
       </c>
       <c r="J84" t="n">
         <v>330</v>
@@ -22607,23 +22792,23 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>31733</v>
+        <v>30931</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.02592867996508357</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F85" t="n">
-        <v>35544</v>
+        <v>35515</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -22632,32 +22817,32 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.0008165563846262143</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>1876</v>
+        <v>330</v>
       </c>
       <c r="K85" t="n">
-        <v>14</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>31876</v>
+        <v>31733</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.004506349856616141</v>
+        <v>0.02592867996508357</v>
       </c>
       <c r="E86" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F86" t="n">
         <v>35544</v>
@@ -22669,35 +22854,35 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0</v>
+        <v>0.0008165563846262143</v>
       </c>
       <c r="J86" t="n">
-        <v>1862</v>
+        <v>1876</v>
       </c>
       <c r="K86" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>32667</v>
+        <v>31876</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.02481490776759945</v>
+        <v>0.004506349856616141</v>
       </c>
       <c r="E87" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F87" t="n">
-        <v>36452</v>
+        <v>35544</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -22706,32 +22891,32 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.02554580238577538</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>1905</v>
+        <v>1862</v>
       </c>
       <c r="K87" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>32713</v>
+        <v>32667</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.001408148896439832</v>
+        <v>0.02481490776759945</v>
       </c>
       <c r="E88" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F88" t="n">
         <v>36452</v>
@@ -22743,109 +22928,109 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0</v>
+        <v>0.02554580238577538</v>
       </c>
       <c r="J88" t="n">
-        <v>1918</v>
+        <v>1905</v>
       </c>
       <c r="K88" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>32844</v>
+        <v>32713</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.00400452419527405</v>
+        <v>0.001408148896439832</v>
       </c>
       <c r="E89" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F89" t="n">
-        <v>35152</v>
+        <v>36452</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>936</v>
+        <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>-0.009985734664764621</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>1938</v>
+        <v>1918</v>
       </c>
       <c r="K89" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>30704</v>
+        <v>32844</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.06515649738156132</v>
+        <v>0.00400452419527405</v>
       </c>
       <c r="E90" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F90" t="n">
-        <v>32196</v>
+        <v>35152</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>936</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.1078474839281756</v>
+        <v>-0.009985734664764621</v>
       </c>
       <c r="J90" t="n">
-        <v>335</v>
+        <v>1938</v>
       </c>
       <c r="K90" t="n">
-        <v>1538</v>
+        <v>32</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>30931</v>
+        <v>30704</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.007393173527879104</v>
+        <v>-0.06515649738156132</v>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F91" t="n">
-        <v>35515</v>
+        <v>32196</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -22854,35 +23039,35 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.1030873400422413</v>
+        <v>-0.1078474839281756</v>
       </c>
       <c r="J91" t="n">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K91" t="n">
-        <v>1548</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>31733</v>
+        <v>30931</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.02592867996508357</v>
+        <v>0.007393173527879104</v>
       </c>
       <c r="E92" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F92" t="n">
-        <v>35544</v>
+        <v>35515</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -22891,32 +23076,32 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.0008165563846262143</v>
+        <v>0.1030873400422413</v>
       </c>
       <c r="J92" t="n">
-        <v>1876</v>
+        <v>330</v>
       </c>
       <c r="K92" t="n">
-        <v>19</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>31876</v>
+        <v>31733</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.004506349856616141</v>
+        <v>0.02592867996508357</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F93" t="n">
         <v>35544</v>
@@ -22928,35 +23113,35 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0</v>
+        <v>0.0008165563846262143</v>
       </c>
       <c r="J93" t="n">
-        <v>1862</v>
+        <v>1876</v>
       </c>
       <c r="K93" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>32667</v>
+        <v>31876</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.02481490776759945</v>
+        <v>0.004506349856616141</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F94" t="n">
-        <v>36452</v>
+        <v>35544</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -22965,32 +23150,32 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0.02554580238577538</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>1900</v>
+        <v>1862</v>
       </c>
       <c r="K94" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>32866</v>
+        <v>32667</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.00609177457372884</v>
+        <v>0.02481490776759945</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F95" t="n">
         <v>36452</v>
@@ -23002,10 +23187,10 @@
         <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0</v>
+        <v>0.02554580238577538</v>
       </c>
       <c r="J95" t="n">
-        <v>1923</v>
+        <v>1900</v>
       </c>
       <c r="K95" t="n">
         <v>1</v>
@@ -23014,59 +23199,96 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>32866</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.00609177457372884</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="n">
+        <v>36452</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>1923</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B97" t="n">
         <v>32844</v>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="n">
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
         <v>-0.0006693847745390373</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>10</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F97" t="n">
         <v>35152</v>
       </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
         <v>936</v>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I97" s="3" t="n">
         <v>-0.009985734664764621</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>1938</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K97" t="n">
         <v>36</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>2140</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>2956</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
         <v>936</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>1603</v>
       </c>
     </row>
@@ -23095,7 +23317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -25811,7 +26033,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -26131,20 +26353,20 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>7129</v>
+        <v>7537</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.05413294414223166</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -26159,26 +26381,26 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>218</v>
+        <v>334</v>
       </c>
       <c r="K82" t="n">
-        <v>229</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>7542</v>
+        <v>7129</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.05793238883433862</v>
+        <v>-0.05413294414223166</v>
       </c>
       <c r="E83" t="n">
         <v>7</v>
@@ -26196,10 +26418,10 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>94</v>
+        <v>218</v>
       </c>
       <c r="K83" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="84">
@@ -26215,7 +26437,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.05793238883433862</v>
       </c>
       <c r="E84" t="n">
         <v>7</v>
@@ -26242,7 +26464,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -26255,7 +26477,7 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -26273,13 +26495,13 @@
         <v>94</v>
       </c>
       <c r="K85" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -26292,7 +26514,7 @@
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -26316,20 +26538,20 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>7537</v>
+        <v>7542</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>-0.0006629541235746487</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -26344,16 +26566,16 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>328</v>
+        <v>94</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -26363,10 +26585,10 @@
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0</v>
+        <v>-0.0006629541235746487</v>
       </c>
       <c r="E88" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -26390,7 +26612,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -26403,7 +26625,7 @@
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -26418,7 +26640,7 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -26427,20 +26649,20 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>7129</v>
+        <v>7537</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.05413294414223166</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -26455,29 +26677,29 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>218</v>
+        <v>329</v>
       </c>
       <c r="K90" t="n">
-        <v>229</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>7542</v>
+        <v>7129</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.05793238883433862</v>
+        <v>-0.05413294414223166</v>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -26492,16 +26714,16 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>94</v>
+        <v>218</v>
       </c>
       <c r="K91" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -26511,10 +26733,10 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.05793238883433862</v>
       </c>
       <c r="E92" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -26532,13 +26754,13 @@
         <v>94</v>
       </c>
       <c r="K92" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -26551,7 +26773,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -26575,20 +26797,20 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>7537</v>
+        <v>7542</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>-0.0006629541235746487</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -26603,16 +26825,16 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>328</v>
+        <v>94</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -26622,10 +26844,10 @@
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0</v>
+        <v>-0.0006629541235746487</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -26649,7 +26871,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -26662,46 +26884,83 @@
         <v>0</v>
       </c>
       <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>328</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>7537</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
         <v>10</v>
       </c>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" t="n">
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
         <v>329</v>
       </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>408</v>
       </c>
-      <c r="F97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="4" t="n">
+      <c r="F98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="4" t="n">
         <v>235</v>
       </c>
     </row>
@@ -26717,7 +26976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -29433,7 +29692,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E73" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F73" t="n">
         <v>27735</v>
@@ -29753,60 +30012,60 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>71267</v>
+        <v>77335</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.07658918344605976</v>
+        <v>0.002034258467438908</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>28259</v>
+        <v>27735</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>462</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.01889309536686497</v>
+        <v>0.01665765278528935</v>
       </c>
       <c r="J82" t="n">
-        <v>3951</v>
+        <v>5401</v>
       </c>
       <c r="K82" t="n">
-        <v>1125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>71432</v>
+        <v>71267</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.002315237066243844</v>
+        <v>-0.07846382621064202</v>
       </c>
       <c r="E83" t="n">
         <v>7</v>
       </c>
       <c r="F83" t="n">
-        <v>27715</v>
+        <v>28259</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -29815,13 +30074,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>-0.01925050426412824</v>
+        <v>0.002198815476823776</v>
       </c>
       <c r="J83" t="n">
-        <v>3944</v>
+        <v>3951</v>
       </c>
       <c r="K83" t="n">
-        <v>1175</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="84">
@@ -29837,7 +30096,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.002315237066243844</v>
       </c>
       <c r="E84" t="n">
         <v>7</v>
@@ -29852,7 +30111,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>-0.01925050426412824</v>
       </c>
       <c r="J84" t="n">
         <v>3944</v>
@@ -29864,20 +30123,20 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>71457</v>
+        <v>71432</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.0003499832008063613</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F85" t="n">
         <v>27715</v>
@@ -29892,16 +30151,16 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>3634</v>
+        <v>3944</v>
       </c>
       <c r="K85" t="n">
-        <v>1531</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -29911,13 +30170,13 @@
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0</v>
+        <v>0.0003499832008063613</v>
       </c>
       <c r="E86" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F86" t="n">
-        <v>27735</v>
+        <v>27715</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -29926,32 +30185,32 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.0007216308858019123</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>5151</v>
+        <v>3634</v>
       </c>
       <c r="K86" t="n">
-        <v>23</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>75678</v>
+        <v>71457</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.05907048994500189</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F87" t="n">
         <v>27735</v>
@@ -29963,32 +30222,32 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0</v>
+        <v>0.0007216308858019123</v>
       </c>
       <c r="J87" t="n">
-        <v>5218</v>
+        <v>5151</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>76307</v>
+        <v>75678</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.008311530431565316</v>
+        <v>0.05907048994500189</v>
       </c>
       <c r="E88" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F88" t="n">
         <v>27735</v>
@@ -30003,29 +30262,29 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>5271</v>
+        <v>5218</v>
       </c>
       <c r="K88" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>77178</v>
+        <v>76307</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.01141441807435753</v>
+        <v>0.008311530431565316</v>
       </c>
       <c r="E89" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F89" t="n">
         <v>27735</v>
@@ -30034,75 +30293,75 @@
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>462</v>
+        <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.01665765278528935</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>5326</v>
+        <v>5271</v>
       </c>
       <c r="K89" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>71267</v>
+        <v>77178</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.07658918344605976</v>
+        <v>0.01141441807435753</v>
       </c>
       <c r="E90" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F90" t="n">
-        <v>28259</v>
+        <v>27735</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>462</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>0.002198815476823776</v>
+        <v>0.01665765278528935</v>
       </c>
       <c r="J90" t="n">
-        <v>3951</v>
+        <v>5326</v>
       </c>
       <c r="K90" t="n">
-        <v>1125</v>
+        <v>11</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>71432</v>
+        <v>71267</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.002315237066243844</v>
+        <v>-0.07658918344605976</v>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F91" t="n">
-        <v>27715</v>
+        <v>28259</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -30111,32 +30370,32 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>-0.01925050426412824</v>
+        <v>0.002198815476823776</v>
       </c>
       <c r="J91" t="n">
-        <v>3944</v>
+        <v>3951</v>
       </c>
       <c r="K91" t="n">
-        <v>1177</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>71457</v>
+        <v>71432</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.0003499832008063613</v>
+        <v>0.002315237066243844</v>
       </c>
       <c r="E92" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F92" t="n">
         <v>27715</v>
@@ -30148,35 +30407,35 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>-0.01925050426412824</v>
       </c>
       <c r="J92" t="n">
-        <v>4079</v>
+        <v>3944</v>
       </c>
       <c r="K92" t="n">
-        <v>1087</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>71542</v>
+        <v>71457</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.001189526568425767</v>
+        <v>0.0003499832008063613</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F93" t="n">
-        <v>27735</v>
+        <v>27715</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -30185,32 +30444,32 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.0007216308858019123</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>5143</v>
+        <v>4079</v>
       </c>
       <c r="K93" t="n">
-        <v>23</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>75689</v>
+        <v>71542</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.0579659500712868</v>
+        <v>0.001189526568425767</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F94" t="n">
         <v>27735</v>
@@ -30222,32 +30481,32 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0</v>
+        <v>0.0007216308858019123</v>
       </c>
       <c r="J94" t="n">
-        <v>5217</v>
+        <v>5143</v>
       </c>
       <c r="K94" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>76918</v>
+        <v>75689</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.01623749818335557</v>
+        <v>0.0579659500712868</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F95" t="n">
         <v>27735</v>
@@ -30262,29 +30521,29 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>5278</v>
+        <v>5217</v>
       </c>
       <c r="K95" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>77178</v>
+        <v>76918</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>0.003380223094724252</v>
+        <v>0.01623749818335557</v>
       </c>
       <c r="E96" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F96" t="n">
         <v>27735</v>
@@ -30293,37 +30552,74 @@
         <v>0</v>
       </c>
       <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>5278</v>
+      </c>
+      <c r="K96" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>77178</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0.003380223094724252</v>
+      </c>
+      <c r="E97" t="n">
+        <v>10</v>
+      </c>
+      <c r="F97" t="n">
+        <v>27735</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
         <v>462</v>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I97" s="3" t="n">
         <v>0.01665765278528935</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>5339</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K97" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>5911</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>-524</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
         <v>462</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>1388</v>
       </c>
     </row>
@@ -30339,7 +30635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -33055,7 +33351,7 @@
         <v>0.0218546156656056</v>
       </c>
       <c r="E73" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F73" t="n">
         <v>62640</v>
@@ -33375,23 +33671,23 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>91098</v>
+        <v>97909</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.05074608202734245</v>
+        <v>0.0202254918306102</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>32196</v>
+        <v>62640</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -33400,35 +33696,35 @@
         <v>0</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.4860153256704981</v>
+        <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>218</v>
+        <v>5484</v>
       </c>
       <c r="K82" t="n">
-        <v>4127</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>91331</v>
+        <v>91098</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.002557685130299238</v>
+        <v>-0.06956459569600343</v>
       </c>
       <c r="E83" t="n">
         <v>7</v>
       </c>
       <c r="F83" t="n">
-        <v>24326</v>
+        <v>32196</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -33437,13 +33733,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>-0.2444403031432476</v>
+        <v>-0.4860153256704981</v>
       </c>
       <c r="J83" t="n">
-        <v>896</v>
+        <v>218</v>
       </c>
       <c r="K83" t="n">
-        <v>4175</v>
+        <v>4127</v>
       </c>
     </row>
     <row r="84">
@@ -33459,7 +33755,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.002557685130299238</v>
       </c>
       <c r="E84" t="n">
         <v>7</v>
@@ -33474,7 +33770,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>-0.2444403031432476</v>
       </c>
       <c r="J84" t="n">
         <v>896</v>
@@ -33486,23 +33782,23 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>93311</v>
+        <v>91331</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.02167938596971455</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F85" t="n">
-        <v>41334</v>
+        <v>24326</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -33511,32 +33807,32 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.6991696127600099</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>5109</v>
+        <v>896</v>
       </c>
       <c r="K85" t="n">
-        <v>22</v>
+        <v>4175</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>94027</v>
+        <v>93311</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.007673264674047004</v>
+        <v>0.02167938596971455</v>
       </c>
       <c r="E86" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F86" t="n">
         <v>41334</v>
@@ -33548,35 +33844,35 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0</v>
+        <v>0.6991696127600099</v>
       </c>
       <c r="J86" t="n">
-        <v>5083</v>
+        <v>5109</v>
       </c>
       <c r="K86" t="n">
-        <v>52</v>
+        <v>22</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>95278</v>
+        <v>94027</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.01330468907866889</v>
+        <v>0.007673264674047004</v>
       </c>
       <c r="E87" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F87" t="n">
-        <v>62640</v>
+        <v>41334</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -33585,32 +33881,32 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.5154594280737408</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>5168</v>
+        <v>5083</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>95409</v>
+        <v>95278</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.001374923906883016</v>
+        <v>0.01330468907866889</v>
       </c>
       <c r="E88" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F88" t="n">
         <v>62640</v>
@@ -33622,32 +33918,32 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0</v>
+        <v>0.5154594280737408</v>
       </c>
       <c r="J88" t="n">
-        <v>5196</v>
+        <v>5168</v>
       </c>
       <c r="K88" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>96022</v>
+        <v>95409</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.006424970390634007</v>
+        <v>0.001374923906883016</v>
       </c>
       <c r="E89" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F89" t="n">
         <v>62640</v>
@@ -33662,32 +33958,32 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>5365</v>
+        <v>5196</v>
       </c>
       <c r="K89" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>91098</v>
+        <v>96022</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.0512799150194747</v>
+        <v>0.006424970390634007</v>
       </c>
       <c r="E90" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F90" t="n">
-        <v>32196</v>
+        <v>62640</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -33696,35 +33992,35 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.4860153256704981</v>
+        <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>218</v>
+        <v>5365</v>
       </c>
       <c r="K90" t="n">
-        <v>4127</v>
+        <v>17</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>91407</v>
+        <v>91098</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.003391951524731608</v>
+        <v>-0.0512799150194747</v>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F91" t="n">
-        <v>24326</v>
+        <v>32196</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -33733,35 +34029,35 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>-0.2444403031432476</v>
+        <v>-0.4860153256704981</v>
       </c>
       <c r="J91" t="n">
-        <v>896</v>
+        <v>218</v>
       </c>
       <c r="K91" t="n">
-        <v>4183</v>
+        <v>4127</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>93311</v>
+        <v>91407</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.02082991455796602</v>
+        <v>0.003391951524731608</v>
       </c>
       <c r="E92" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F92" t="n">
-        <v>41334</v>
+        <v>24326</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -33770,32 +34066,32 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.6991696127600099</v>
+        <v>-0.2444403031432476</v>
       </c>
       <c r="J92" t="n">
-        <v>5108</v>
+        <v>896</v>
       </c>
       <c r="K92" t="n">
-        <v>26</v>
+        <v>4183</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>95633</v>
+        <v>93311</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.02488452594013568</v>
+        <v>0.02082991455796602</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F93" t="n">
         <v>41334</v>
@@ -33807,35 +34103,35 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0</v>
+        <v>0.6991696127600099</v>
       </c>
       <c r="J93" t="n">
-        <v>5082</v>
+        <v>5108</v>
       </c>
       <c r="K93" t="n">
-        <v>52</v>
+        <v>26</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>95278</v>
+        <v>95633</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>-0.003712107745234386</v>
+        <v>0.02488452594013568</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F94" t="n">
-        <v>62640</v>
+        <v>41334</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -33844,32 +34140,32 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0.5154594280737408</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>5172</v>
+        <v>5082</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>95409</v>
+        <v>95278</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.001374923906883016</v>
+        <v>-0.003712107745234386</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F95" t="n">
         <v>62640</v>
@@ -33881,32 +34177,32 @@
         <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0</v>
+        <v>0.5154594280737408</v>
       </c>
       <c r="J95" t="n">
-        <v>5211</v>
+        <v>5172</v>
       </c>
       <c r="K95" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>96022</v>
+        <v>95409</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>0.006424970390634007</v>
+        <v>0.001374923906883016</v>
       </c>
       <c r="E96" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F96" t="n">
         <v>62640</v>
@@ -33921,31 +34217,68 @@
         <v>0</v>
       </c>
       <c r="J96" t="n">
+        <v>5211</v>
+      </c>
+      <c r="K96" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>96022</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0.006424970390634007</v>
+      </c>
+      <c r="E97" t="n">
+        <v>10</v>
+      </c>
+      <c r="F97" t="n">
+        <v>62640</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
         <v>5394</v>
       </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>4924</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>30444</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="4" t="n">
         <v>5394</v>
       </c>
     </row>
@@ -33961,7 +34294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -36677,7 +37010,7 @@
         <v>0.008278113896091423</v>
       </c>
       <c r="E73" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F73" t="n">
         <v>5327</v>
@@ -36997,60 +37330,60 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>91775</v>
+        <v>104992</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.1186497647171804</v>
+        <v>0.008278113896091423</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>2879</v>
+        <v>5327</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>94788</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.00826730967964175</v>
+        <v>33.48673785738891</v>
       </c>
       <c r="J82" t="n">
-        <v>505</v>
+        <v>5585</v>
       </c>
       <c r="K82" t="n">
-        <v>3851</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>94512</v>
+        <v>91775</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.02982293652955598</v>
+        <v>-0.1258857817738494</v>
       </c>
       <c r="E83" t="n">
         <v>7</v>
       </c>
       <c r="F83" t="n">
-        <v>2903</v>
+        <v>2879</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -37059,13 +37392,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.008336227856894755</v>
+        <v>-0.9712430704689607</v>
       </c>
       <c r="J83" t="n">
         <v>505</v>
       </c>
       <c r="K83" t="n">
-        <v>4025</v>
+        <v>3851</v>
       </c>
     </row>
     <row r="84">
@@ -37081,7 +37414,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.02982293652955598</v>
       </c>
       <c r="E84" t="n">
         <v>7</v>
@@ -37096,7 +37429,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>0.008336227856894755</v>
       </c>
       <c r="J84" t="n">
         <v>505</v>
@@ -37108,20 +37441,20 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>101257</v>
+        <v>94512</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.07136659895039783</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F85" t="n">
         <v>2903</v>
@@ -37139,29 +37472,29 @@
         <v>505</v>
       </c>
       <c r="K85" t="n">
-        <v>4300</v>
+        <v>4025</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>104594</v>
+        <v>101257</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.03295574626939372</v>
+        <v>0.07136659895039783</v>
       </c>
       <c r="E86" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F86" t="n">
-        <v>128535</v>
+        <v>2903</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -37170,32 +37503,32 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>43.27661040303135</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>4737</v>
+        <v>505</v>
       </c>
       <c r="K86" t="n">
-        <v>36</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>104147</v>
+        <v>104594</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>-0.004273667705604528</v>
+        <v>0.03295574626939372</v>
       </c>
       <c r="E87" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F87" t="n">
         <v>128535</v>
@@ -37207,35 +37540,35 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0</v>
+        <v>43.27661040303135</v>
       </c>
       <c r="J87" t="n">
-        <v>4944</v>
+        <v>4737</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>104305</v>
+        <v>104147</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.001517086425917213</v>
+        <v>-0.004273667705604528</v>
       </c>
       <c r="E88" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F88" t="n">
-        <v>2903</v>
+        <v>128535</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -37244,32 +37577,32 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>-0.9774147119461625</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>5159</v>
+        <v>4944</v>
       </c>
       <c r="K88" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>104130</v>
+        <v>104305</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>-0.001677771918891712</v>
+        <v>0.001517086425917213</v>
       </c>
       <c r="E89" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F89" t="n">
         <v>2903</v>
@@ -37281,35 +37614,35 @@
         <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0</v>
+        <v>-0.9774147119461625</v>
       </c>
       <c r="J89" t="n">
-        <v>5445</v>
+        <v>5159</v>
       </c>
       <c r="K89" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>91775</v>
+        <v>104130</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.1186497647171804</v>
+        <v>-0.001677771918891712</v>
       </c>
       <c r="E90" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F90" t="n">
-        <v>2879</v>
+        <v>2903</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -37318,35 +37651,35 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.00826730967964175</v>
+        <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>505</v>
+        <v>5445</v>
       </c>
       <c r="K90" t="n">
-        <v>3851</v>
+        <v>11</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>94387</v>
+        <v>91775</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.02846090983383274</v>
+        <v>-0.1186497647171804</v>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F91" t="n">
-        <v>2903</v>
+        <v>2879</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -37355,32 +37688,32 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.008336227856894755</v>
+        <v>-0.00826730967964175</v>
       </c>
       <c r="J91" t="n">
         <v>505</v>
       </c>
       <c r="K91" t="n">
-        <v>4043</v>
+        <v>3851</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>101076</v>
+        <v>94387</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.07086781018572473</v>
+        <v>0.02846090983383274</v>
       </c>
       <c r="E92" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F92" t="n">
         <v>2903</v>
@@ -37392,35 +37725,35 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.008336227856894755</v>
       </c>
       <c r="J92" t="n">
         <v>505</v>
       </c>
       <c r="K92" t="n">
-        <v>4312</v>
+        <v>4043</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>102786</v>
+        <v>101076</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.01691796272112074</v>
+        <v>0.07086781018572473</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F93" t="n">
-        <v>128535</v>
+        <v>2903</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -37429,35 +37762,35 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>43.27661040303135</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>4731</v>
+        <v>505</v>
       </c>
       <c r="K93" t="n">
-        <v>73</v>
+        <v>4312</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>104147</v>
+        <v>102786</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.01324110287393225</v>
+        <v>0.01691796272112074</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F94" t="n">
-        <v>2903</v>
+        <v>128535</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -37466,32 +37799,32 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>-0.9774147119461625</v>
+        <v>43.27661040303135</v>
       </c>
       <c r="J94" t="n">
-        <v>4954</v>
+        <v>4731</v>
       </c>
       <c r="K94" t="n">
-        <v>12</v>
+        <v>73</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>104366</v>
+        <v>104147</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.002102797008075125</v>
+        <v>0.01324110287393225</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F95" t="n">
         <v>2903</v>
@@ -37503,32 +37836,32 @@
         <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0</v>
+        <v>-0.9774147119461625</v>
       </c>
       <c r="J95" t="n">
-        <v>5166</v>
+        <v>4954</v>
       </c>
       <c r="K95" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>104986</v>
+        <v>104366</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>0.005940632006592186</v>
+        <v>0.002102797008075125</v>
       </c>
       <c r="E96" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F96" t="n">
         <v>2903</v>
@@ -37543,31 +37876,68 @@
         <v>0</v>
       </c>
       <c r="J96" t="n">
+        <v>5166</v>
+      </c>
+      <c r="K96" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>104986</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0.005940632006592186</v>
+      </c>
+      <c r="E97" t="n">
+        <v>10</v>
+      </c>
+      <c r="F97" t="n">
+        <v>2903</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
         <v>5464</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K97" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>13211</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="4" t="n">
         <v>4959</v>
       </c>
     </row>
@@ -37583,7 +37953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -40299,7 +40669,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E73" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -40619,20 +40989,20 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3460</v>
+        <v>6613</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.4715943799633476</v>
+        <v>0.009926695174098962</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -40647,16 +41017,16 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>283</v>
+        <v>321</v>
       </c>
       <c r="K82" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -40666,7 +41036,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0</v>
+        <v>-0.4767881445637381</v>
       </c>
       <c r="E83" t="n">
         <v>7</v>
@@ -40684,10 +41054,10 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
     </row>
     <row r="84">
@@ -40730,7 +41100,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -40743,7 +41113,7 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -40761,26 +41131,26 @@
         <v>281</v>
       </c>
       <c r="K85" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>3327</v>
+        <v>3460</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>-0.0384393063583815</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -40804,20 +41174,20 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2498</v>
+        <v>3327</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>-0.2491734295160805</v>
+        <v>-0.0384393063583815</v>
       </c>
       <c r="E87" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -40832,29 +41202,29 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>6548</v>
+        <v>2498</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>1.621297037630104</v>
+        <v>-0.2491734295160805</v>
       </c>
       <c r="E88" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -40869,7 +41239,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>314</v>
+        <v>285</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -40878,7 +41248,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -40888,10 +41258,10 @@
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0</v>
+        <v>1.621297037630104</v>
       </c>
       <c r="E89" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -40906,29 +41276,29 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="K89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>3460</v>
+        <v>6548</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.4715943799633476</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -40943,16 +41313,16 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>283</v>
+        <v>316</v>
       </c>
       <c r="K90" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -40962,10 +41332,10 @@
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>-0.4715943799633476</v>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -40980,16 +41350,16 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K91" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -41002,7 +41372,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -41020,26 +41390,26 @@
         <v>281</v>
       </c>
       <c r="K92" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>3327</v>
+        <v>3460</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>-0.0384393063583815</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -41063,57 +41433,57 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>2498</v>
+        <v>3327</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>-0.2491734295160805</v>
+        <v>-0.0384393063583815</v>
       </c>
       <c r="E94" t="n">
+        <v>6</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>281</v>
+      </c>
+      <c r="K94" t="n">
         <v>4</v>
-      </c>
-      <c r="F94" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" t="n">
-        <v>0</v>
-      </c>
-      <c r="H94" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" t="n">
-        <v>285</v>
-      </c>
-      <c r="K94" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>6548</v>
+        <v>2498</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>1.621297037630104</v>
+        <v>-0.2491734295160805</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -41128,16 +41498,16 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>314</v>
+        <v>285</v>
       </c>
       <c r="K95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -41147,49 +41517,86 @@
         <v>0</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>0</v>
+        <v>1.621297037630104</v>
       </c>
       <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>314</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>6548</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
         <v>10</v>
       </c>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" t="n">
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
         <v>317</v>
       </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>3088</v>
       </c>
-      <c r="F97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="4" t="n">
+      <c r="F98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="4" t="n">
         <v>34</v>
       </c>
     </row>
@@ -41205,7 +41612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -43921,7 +44328,7 @@
         <v>0.07789955604883463</v>
       </c>
       <c r="E73" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F73" t="n">
         <v>19648</v>
@@ -44241,60 +44648,60 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>13639</v>
+        <v>15539</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.0538984461709212</v>
+        <v>0.07789955604883463</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>6042</v>
+        <v>19648</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>277</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.6605808662434695</v>
+        <v>0.1193191393741925</v>
       </c>
       <c r="J82" t="n">
-        <v>661</v>
+        <v>789</v>
       </c>
       <c r="K82" t="n">
-        <v>182</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>13748</v>
+        <v>13639</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.00799178825427084</v>
+        <v>-0.1222729905399318</v>
       </c>
       <c r="E83" t="n">
         <v>7</v>
       </c>
       <c r="F83" t="n">
-        <v>16544</v>
+        <v>6042</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -44303,13 +44710,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>1.738166170142337</v>
+        <v>-0.696762860727729</v>
       </c>
       <c r="J83" t="n">
-        <v>639</v>
+        <v>661</v>
       </c>
       <c r="K83" t="n">
-        <v>81</v>
+        <v>182</v>
       </c>
     </row>
     <row r="84">
@@ -44325,7 +44732,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.00799178825427084</v>
       </c>
       <c r="E84" t="n">
         <v>7</v>
@@ -44340,7 +44747,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>1.738166170142337</v>
       </c>
       <c r="J84" t="n">
         <v>639</v>
@@ -44352,23 +44759,23 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>13808</v>
+        <v>13748</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.004364271166715158</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F85" t="n">
-        <v>17801</v>
+        <v>16544</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -44377,19 +44784,19 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.07597920696324952</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>718</v>
+        <v>639</v>
       </c>
       <c r="K85" t="n">
-        <v>6</v>
+        <v>81</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -44399,10 +44806,10 @@
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0</v>
+        <v>0.004364271166715158</v>
       </c>
       <c r="E86" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F86" t="n">
         <v>17801</v>
@@ -44414,32 +44821,32 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0</v>
+        <v>0.07597920696324952</v>
       </c>
       <c r="J86" t="n">
         <v>718</v>
       </c>
       <c r="K86" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>14199</v>
+        <v>13808</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.02831691772885284</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F87" t="n">
         <v>17801</v>
@@ -44454,29 +44861,29 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>869</v>
+        <v>718</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>14323</v>
+        <v>14199</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.008733009366856821</v>
+        <v>0.02831691772885284</v>
       </c>
       <c r="E88" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F88" t="n">
         <v>17801</v>
@@ -44491,29 +44898,29 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>762</v>
+        <v>869</v>
       </c>
       <c r="K88" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>14416</v>
+        <v>14323</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.006493053131327236</v>
+        <v>0.008733009366856821</v>
       </c>
       <c r="E89" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F89" t="n">
         <v>17801</v>
@@ -44522,75 +44929,75 @@
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>277</v>
+        <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.01556092354362115</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>777</v>
+        <v>762</v>
       </c>
       <c r="K89" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>13639</v>
+        <v>14416</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.0538984461709212</v>
+        <v>0.006493053131327236</v>
       </c>
       <c r="E90" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F90" t="n">
-        <v>6042</v>
+        <v>17801</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>277</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.6657816130102887</v>
+        <v>0.01556092354362115</v>
       </c>
       <c r="J90" t="n">
-        <v>661</v>
+        <v>777</v>
       </c>
       <c r="K90" t="n">
-        <v>182</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>13748</v>
+        <v>13639</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.00799178825427084</v>
+        <v>-0.0538984461709212</v>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F91" t="n">
-        <v>17801</v>
+        <v>6042</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -44599,32 +45006,32 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>1.94620986428335</v>
+        <v>-0.6657816130102887</v>
       </c>
       <c r="J91" t="n">
-        <v>639</v>
+        <v>661</v>
       </c>
       <c r="K91" t="n">
-        <v>81</v>
+        <v>182</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>13808</v>
+        <v>13748</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.004364271166715158</v>
+        <v>0.00799178825427084</v>
       </c>
       <c r="E92" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F92" t="n">
         <v>17801</v>
@@ -44636,19 +45043,19 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.94620986428335</v>
       </c>
       <c r="J92" t="n">
-        <v>718</v>
+        <v>639</v>
       </c>
       <c r="K92" t="n">
-        <v>6</v>
+        <v>81</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -44658,10 +45065,10 @@
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0</v>
+        <v>0.004364271166715158</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F93" t="n">
         <v>17801</v>
@@ -44676,29 +45083,29 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="K93" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>14199</v>
+        <v>13808</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.02831691772885284</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F94" t="n">
         <v>17801</v>
@@ -44713,29 +45120,29 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>869</v>
+        <v>717</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>14323</v>
+        <v>14199</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.008733009366856821</v>
+        <v>0.02831691772885284</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F95" t="n">
         <v>17801</v>
@@ -44750,7 +45157,7 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>767</v>
+        <v>869</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -44759,20 +45166,20 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>14397</v>
+        <v>14323</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>0.005166515394819521</v>
+        <v>0.008733009366856821</v>
       </c>
       <c r="E96" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F96" t="n">
         <v>17801</v>
@@ -44781,37 +45188,74 @@
         <v>0</v>
       </c>
       <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>767</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>14397</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0.005166515394819521</v>
+      </c>
+      <c r="E97" t="n">
+        <v>10</v>
+      </c>
+      <c r="F97" t="n">
+        <v>17801</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
         <v>277</v>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I97" s="3" t="n">
         <v>0.01556092354362115</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>783</v>
       </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>758</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>11759</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
         <v>277</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>122</v>
       </c>
     </row>
@@ -44827,7 +45271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -47543,7 +47987,7 @@
         <v>0.07516970469659902</v>
       </c>
       <c r="E73" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F73" t="n">
         <v>18686</v>
@@ -47863,60 +48307,60 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>57724</v>
+        <v>62405</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.005804240367888945</v>
+        <v>0.07481786397065156</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>15094</v>
+        <v>18686</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>26840</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.1917103994859163</v>
+        <v>1.437935096926207</v>
       </c>
       <c r="J82" t="n">
-        <v>703</v>
+        <v>3025</v>
       </c>
       <c r="K82" t="n">
-        <v>1957</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>59299</v>
+        <v>57724</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.02728501143371908</v>
+        <v>-0.07501001522313917</v>
       </c>
       <c r="E83" t="n">
         <v>7</v>
       </c>
       <c r="F83" t="n">
-        <v>18669</v>
+        <v>15094</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -47925,13 +48369,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.2368490791042799</v>
+        <v>-0.6684531915828318</v>
       </c>
       <c r="J83" t="n">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="K83" t="n">
-        <v>1970</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="84">
@@ -47947,7 +48391,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.02728501143371908</v>
       </c>
       <c r="E84" t="n">
         <v>7</v>
@@ -47962,7 +48406,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>0.2368490791042799</v>
       </c>
       <c r="J84" t="n">
         <v>701</v>
@@ -47974,20 +48418,20 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>59606</v>
+        <v>59299</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.005177153071721277</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F85" t="n">
         <v>18669</v>
@@ -48005,13 +48449,13 @@
         <v>701</v>
       </c>
       <c r="K85" t="n">
-        <v>2042</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -48021,10 +48465,10 @@
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0</v>
+        <v>0.005177153071721277</v>
       </c>
       <c r="E86" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F86" t="n">
         <v>18669</v>
@@ -48039,32 +48483,32 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>1780</v>
+        <v>701</v>
       </c>
       <c r="K86" t="n">
-        <v>1024</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>56255</v>
+        <v>59606</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>-0.05621917256652015</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F87" t="n">
-        <v>18674</v>
+        <v>18669</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -48073,32 +48517,32 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.0002678236648990305</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>2827</v>
+        <v>1780</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>57038</v>
+        <v>56255</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.01391876277664208</v>
+        <v>-0.05621917256652015</v>
       </c>
       <c r="E88" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F88" t="n">
         <v>18674</v>
@@ -48110,32 +48554,32 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0</v>
+        <v>0.0002678236648990305</v>
       </c>
       <c r="J88" t="n">
-        <v>2890</v>
+        <v>2827</v>
       </c>
       <c r="K88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>58061</v>
+        <v>57038</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.01793541148006592</v>
+        <v>0.01391876277664208</v>
       </c>
       <c r="E89" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F89" t="n">
         <v>18674</v>
@@ -48144,75 +48588,75 @@
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>14885</v>
+        <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.7970975688122524</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>2936</v>
+        <v>2890</v>
       </c>
       <c r="K89" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>57724</v>
+        <v>58061</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.005804240367888945</v>
+        <v>0.01793541148006592</v>
       </c>
       <c r="E90" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F90" t="n">
-        <v>15094</v>
+        <v>18674</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>14885</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.5502249769063441</v>
+        <v>0.7970975688122524</v>
       </c>
       <c r="J90" t="n">
-        <v>703</v>
+        <v>2936</v>
       </c>
       <c r="K90" t="n">
-        <v>1957</v>
+        <v>15</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>59299</v>
+        <v>57724</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.02728501143371908</v>
+        <v>-0.005804240367888945</v>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F91" t="n">
-        <v>18669</v>
+        <v>15094</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -48221,32 +48665,32 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.2368490791042799</v>
+        <v>-0.5502249769063441</v>
       </c>
       <c r="J91" t="n">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="K91" t="n">
-        <v>1974</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>59606</v>
+        <v>59299</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.005177153071721277</v>
+        <v>0.02728501143371908</v>
       </c>
       <c r="E92" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F92" t="n">
         <v>18669</v>
@@ -48258,19 +48702,19 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.2368490791042799</v>
       </c>
       <c r="J92" t="n">
         <v>701</v>
       </c>
       <c r="K92" t="n">
-        <v>2044</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -48280,13 +48724,13 @@
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0</v>
+        <v>0.005177153071721277</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F93" t="n">
-        <v>18674</v>
+        <v>18669</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -48295,32 +48739,32 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.0002678236648990305</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>1843</v>
+        <v>701</v>
       </c>
       <c r="K93" t="n">
-        <v>951</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>56255</v>
+        <v>59606</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>-0.05621917256652015</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F94" t="n">
         <v>18674</v>
@@ -48332,32 +48776,32 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0</v>
+        <v>0.0002678236648990305</v>
       </c>
       <c r="J94" t="n">
-        <v>2833</v>
+        <v>1843</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>951</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>57038</v>
+        <v>56255</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.01391876277664208</v>
+        <v>-0.05621917256652015</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F95" t="n">
         <v>18674</v>
@@ -48372,29 +48816,29 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>2891</v>
+        <v>2833</v>
       </c>
       <c r="K95" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>58061</v>
+        <v>57038</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>0.01793541148006592</v>
+        <v>0.01391876277664208</v>
       </c>
       <c r="E96" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F96" t="n">
         <v>18674</v>
@@ -48403,37 +48847,74 @@
         <v>0</v>
       </c>
       <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>2891</v>
+      </c>
+      <c r="K96" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>58061</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0.01793541148006592</v>
+      </c>
+      <c r="E97" t="n">
+        <v>10</v>
+      </c>
+      <c r="F97" t="n">
+        <v>18674</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
         <v>14885</v>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I97" s="3" t="n">
         <v>0.7970975688122524</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>2962</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K97" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>337</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>3580</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
         <v>14885</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>2259</v>
       </c>
     </row>
@@ -48449,7 +48930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -51165,7 +51646,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -51485,20 +51966,20 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>9237</v>
+        <v>8840</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.04490950226244344</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -51513,16 +51994,16 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>218</v>
+        <v>428</v>
       </c>
       <c r="K82" t="n">
-        <v>341</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -51532,7 +52013,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0</v>
+        <v>0.04490950226244344</v>
       </c>
       <c r="E83" t="n">
         <v>7</v>
@@ -51550,10 +52031,10 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>16</v>
+        <v>218</v>
       </c>
       <c r="K83" t="n">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="84">
@@ -51596,7 +52077,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -51609,7 +52090,7 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -51633,20 +52114,20 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>9228</v>
+        <v>9237</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>-0.000974342318934719</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -51664,26 +52145,26 @@
         <v>16</v>
       </c>
       <c r="K86" t="n">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>7664</v>
+        <v>9228</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>-0.1694841785869094</v>
+        <v>-0.000974342318934719</v>
       </c>
       <c r="E87" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -51698,29 +52179,29 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>369</v>
+        <v>16</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>347</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>8269</v>
+        <v>7664</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.07894050104384133</v>
+        <v>-0.1694841785869094</v>
       </c>
       <c r="E88" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -51735,29 +52216,29 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>391</v>
+        <v>369</v>
       </c>
       <c r="K88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>8840</v>
+        <v>8269</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.06905308985367034</v>
+        <v>0.07894050104384133</v>
       </c>
       <c r="E89" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -51772,29 +52253,29 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>9237</v>
+        <v>8840</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0.04490950226244344</v>
+        <v>0.06905308985367034</v>
       </c>
       <c r="E90" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -51809,16 +52290,16 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>218</v>
+        <v>405</v>
       </c>
       <c r="K90" t="n">
-        <v>341</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -51828,10 +52309,10 @@
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>0.04490950226244344</v>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -51846,16 +52327,16 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>16</v>
+        <v>218</v>
       </c>
       <c r="K91" t="n">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -51868,7 +52349,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -51892,20 +52373,20 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>9228</v>
+        <v>9237</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>-0.000974342318934719</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -51923,26 +52404,26 @@
         <v>16</v>
       </c>
       <c r="K93" t="n">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>7664</v>
+        <v>9228</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>-0.1694841785869094</v>
+        <v>-0.000974342318934719</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -51957,29 +52438,29 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>369</v>
+        <v>16</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>347</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>8269</v>
+        <v>7664</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.07894050104384133</v>
+        <v>-0.1694841785869094</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -51994,68 +52475,105 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>393</v>
+        <v>369</v>
       </c>
       <c r="K95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>8269</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.07894050104384133</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>393</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B97" t="n">
         <v>8840</v>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="n">
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
         <v>0.06905308985367034</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>10</v>
       </c>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" t="n">
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
         <v>405</v>
       </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>-397</v>
       </c>
-      <c r="F97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="4" t="n">
+      <c r="F98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="4" t="n">
         <v>389</v>
       </c>
     </row>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4417,7 +4417,7 @@
         <v>11849</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -8073,7 +8073,7 @@
         <v>-0.001172195522213105</v>
       </c>
       <c r="J82" t="n">
-        <v>8222</v>
+        <v>8221</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -11735,7 +11735,7 @@
         <v>30871</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
@@ -33702,7 +33702,7 @@
         <v>5484</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -37361,7 +37361,7 @@
         <v>5585</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -48338,7 +48338,7 @@
         <v>3025</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4417,7 +4417,7 @@
         <v>11849</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -11735,7 +11735,7 @@
         <v>30871</v>
       </c>
       <c r="K82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -41020,7 +41020,7 @@
         <v>321</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4399,7 +4399,7 @@
         <v>1.71826226409691e-05</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>90046</v>
@@ -8058,7 +8058,7 @@
         <v>0.03114112002966557</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>51126</v>
@@ -11717,7 +11717,7 @@
         <v>0.0136672703849116</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>216983</v>
@@ -15376,7 +15376,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -19035,7 +19035,7 @@
         <v>0.0004012911105295298</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>8026</v>
@@ -22694,7 +22694,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>35152</v>
@@ -26366,7 +26366,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -30025,7 +30025,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>27735</v>
@@ -33684,7 +33684,7 @@
         <v>0.0202254918306102</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>62640</v>
@@ -37343,7 +37343,7 @@
         <v>0.008278113896091423</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>5327</v>
@@ -41002,7 +41002,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -44661,7 +44661,7 @@
         <v>0.07789955604883463</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>19648</v>
@@ -48320,7 +48320,7 @@
         <v>0.07481786397065156</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>18686</v>
@@ -51979,7 +51979,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4417,7 +4417,7 @@
         <v>11849</v>
       </c>
       <c r="K82" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83">
@@ -48338,7 +48338,7 @@
         <v>3025</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4399,7 +4399,7 @@
         <v>1.71826226409691e-05</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>90046</v>
@@ -4417,7 +4417,7 @@
         <v>11849</v>
       </c>
       <c r="K82" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83">
@@ -8058,7 +8058,7 @@
         <v>0.03114112002966557</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>51126</v>
@@ -11717,7 +11717,7 @@
         <v>0.0136672703849116</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>216983</v>
@@ -11735,7 +11735,7 @@
         <v>30871</v>
       </c>
       <c r="K82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
@@ -15376,7 +15376,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -19035,7 +19035,7 @@
         <v>0.0004012911105295298</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>8026</v>
@@ -22694,7 +22694,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>35152</v>
@@ -26366,7 +26366,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -30025,7 +30025,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>27735</v>
@@ -33684,7 +33684,7 @@
         <v>0.0202254918306102</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>62640</v>
@@ -33702,7 +33702,7 @@
         <v>5484</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -37343,7 +37343,7 @@
         <v>0.008278113896091423</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>5327</v>
@@ -41002,7 +41002,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -44661,7 +44661,7 @@
         <v>0.07789955604883463</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>19648</v>
@@ -48320,7 +48320,7 @@
         <v>0.07481786397065156</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>18686</v>
@@ -51979,7 +51979,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4417,7 +4417,7 @@
         <v>11849</v>
       </c>
       <c r="K82" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="83">
@@ -11735,7 +11735,7 @@
         <v>30871</v>
       </c>
       <c r="K82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83">
@@ -33702,7 +33702,7 @@
         <v>5484</v>
       </c>
       <c r="K82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
@@ -37361,7 +37361,7 @@
         <v>5585</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -48338,7 +48338,7 @@
         <v>3025</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4417,7 +4417,7 @@
         <v>11849</v>
       </c>
       <c r="K82" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83">
@@ -8076,7 +8076,7 @@
         <v>8221</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -11735,7 +11735,7 @@
         <v>30871</v>
       </c>
       <c r="K82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83">
@@ -33702,7 +33702,7 @@
         <v>5484</v>
       </c>
       <c r="K82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -37361,7 +37361,7 @@
         <v>5585</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -11735,7 +11735,7 @@
         <v>30871</v>
       </c>
       <c r="K82" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83">
@@ -19053,7 +19053,7 @@
         <v>3706</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -30043,7 +30043,7 @@
         <v>5401</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -48323,16 +48323,16 @@
         <v>2</v>
       </c>
       <c r="F82" t="n">
-        <v>18686</v>
+        <v>18745</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>26840</v>
+        <v>0</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>1.437935096926207</v>
+        <v>0.003802077755167613</v>
       </c>
       <c r="J82" t="n">
         <v>3025</v>
@@ -48369,7 +48369,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>-0.6684531915828318</v>
+        <v>-0.1947719391837824</v>
       </c>
       <c r="J83" t="n">
         <v>703</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4417,7 +4417,7 @@
         <v>11849</v>
       </c>
       <c r="K82" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83">
@@ -8076,7 +8076,7 @@
         <v>8221</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -11735,7 +11735,7 @@
         <v>30871</v>
       </c>
       <c r="K82" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83">
@@ -33702,7 +33702,7 @@
         <v>5484</v>
       </c>
       <c r="K82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
@@ -48338,7 +48338,7 @@
         <v>3025</v>
       </c>
       <c r="K82" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4417,7 +4417,7 @@
         <v>11849</v>
       </c>
       <c r="K82" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="83">
@@ -8076,7 +8076,7 @@
         <v>8221</v>
       </c>
       <c r="K82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
@@ -11735,7 +11735,7 @@
         <v>30871</v>
       </c>
       <c r="K82" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83">
@@ -30043,7 +30043,7 @@
         <v>5401</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -37361,7 +37361,7 @@
         <v>5585</v>
       </c>
       <c r="K82" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -11735,7 +11735,7 @@
         <v>30871</v>
       </c>
       <c r="K82" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="83">
@@ -19053,7 +19053,7 @@
         <v>3706</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -30043,7 +30043,7 @@
         <v>5401</v>
       </c>
       <c r="K82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4399,7 +4399,7 @@
         <v>1.71826226409691e-05</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>90046</v>
@@ -8058,7 +8058,7 @@
         <v>0.03114112002966557</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>51126</v>
@@ -8076,7 +8076,7 @@
         <v>8221</v>
       </c>
       <c r="K82" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83">
@@ -11717,7 +11717,7 @@
         <v>0.0136672703849116</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>216983</v>
@@ -11735,7 +11735,7 @@
         <v>30871</v>
       </c>
       <c r="K82" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83">
@@ -15376,7 +15376,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -19035,7 +19035,7 @@
         <v>0.0004012911105295298</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>8026</v>
@@ -22694,7 +22694,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>35152</v>
@@ -26366,7 +26366,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -30025,7 +30025,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>27735</v>
@@ -30043,7 +30043,7 @@
         <v>5401</v>
       </c>
       <c r="K82" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
@@ -33684,7 +33684,7 @@
         <v>0.0202254918306102</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>62640</v>
@@ -33702,7 +33702,7 @@
         <v>5484</v>
       </c>
       <c r="K82" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83">
@@ -37343,7 +37343,7 @@
         <v>0.008278113896091423</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>5327</v>
@@ -37361,7 +37361,7 @@
         <v>5585</v>
       </c>
       <c r="K82" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83">
@@ -41002,7 +41002,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -44661,7 +44661,7 @@
         <v>0.07789955604883463</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>19648</v>
@@ -48320,7 +48320,7 @@
         <v>0.07481786397065156</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>18745</v>
@@ -51979,7 +51979,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4417,7 +4417,7 @@
         <v>11849</v>
       </c>
       <c r="K82" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="83">
@@ -8076,7 +8076,7 @@
         <v>8221</v>
       </c>
       <c r="K82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="83">
@@ -11735,7 +11735,7 @@
         <v>30871</v>
       </c>
       <c r="K82" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="83">
@@ -15394,7 +15394,7 @@
         <v>1714</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -30043,7 +30043,7 @@
         <v>5401</v>
       </c>
       <c r="K82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83">
@@ -33702,7 +33702,7 @@
         <v>5484</v>
       </c>
       <c r="K82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83">
@@ -37361,7 +37361,7 @@
         <v>5585</v>
       </c>
       <c r="K82" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4399,7 +4399,7 @@
         <v>1.71826226409691e-05</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>90046</v>
@@ -8058,7 +8058,7 @@
         <v>0.03114112002966557</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>51126</v>
@@ -11717,7 +11717,7 @@
         <v>0.0136672703849116</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>216983</v>
@@ -11735,7 +11735,7 @@
         <v>30871</v>
       </c>
       <c r="K82" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="83">
@@ -15376,7 +15376,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -19035,7 +19035,7 @@
         <v>0.0004012911105295298</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>8026</v>
@@ -22694,7 +22694,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>35152</v>
@@ -26366,7 +26366,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -30025,7 +30025,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>27735</v>
@@ -33684,7 +33684,7 @@
         <v>0.0202254918306102</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>62640</v>
@@ -37343,7 +37343,7 @@
         <v>0.008278113896091423</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>5327</v>
@@ -41002,7 +41002,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -44661,7 +44661,7 @@
         <v>0.07789955604883463</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>19648</v>
@@ -48320,7 +48320,7 @@
         <v>0.07481786397065156</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>18745</v>
@@ -51979,7 +51979,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4399,7 +4399,7 @@
         <v>1.71826226409691e-05</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>90046</v>
@@ -8058,7 +8058,7 @@
         <v>0.03114112002966557</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>51126</v>
@@ -11717,7 +11717,7 @@
         <v>0.0136672703849116</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>216983</v>
@@ -11735,7 +11735,7 @@
         <v>30871</v>
       </c>
       <c r="K82" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="83">
@@ -15376,7 +15376,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -19035,7 +19035,7 @@
         <v>0.0004012911105295298</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>8026</v>
@@ -22694,7 +22694,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>35152</v>
@@ -26366,7 +26366,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -30025,7 +30025,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>27735</v>
@@ -30043,7 +30043,7 @@
         <v>5401</v>
       </c>
       <c r="K82" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83">
@@ -33684,7 +33684,7 @@
         <v>0.0202254918306102</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>62640</v>
@@ -37343,7 +37343,7 @@
         <v>0.008278113896091423</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>5327</v>
@@ -37361,7 +37361,7 @@
         <v>5585</v>
       </c>
       <c r="K82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83">
@@ -41002,7 +41002,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -44661,7 +44661,7 @@
         <v>0.07789955604883463</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>19648</v>
@@ -48320,7 +48320,7 @@
         <v>0.07481786397065156</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>18745</v>
@@ -51979,7 +51979,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4399,7 +4399,7 @@
         <v>1.71826226409691e-05</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>90046</v>
@@ -4417,7 +4417,7 @@
         <v>11849</v>
       </c>
       <c r="K82" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="83">
@@ -8058,7 +8058,7 @@
         <v>0.03114112002966557</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>51126</v>
@@ -8076,7 +8076,7 @@
         <v>8221</v>
       </c>
       <c r="K82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83">
@@ -11717,7 +11717,7 @@
         <v>0.0136672703849116</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>216983</v>
@@ -11735,7 +11735,7 @@
         <v>30871</v>
       </c>
       <c r="K82" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="83">
@@ -15376,7 +15376,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -19035,7 +19035,7 @@
         <v>0.0004012911105295298</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>8026</v>
@@ -22694,7 +22694,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>35152</v>
@@ -26366,7 +26366,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -30025,7 +30025,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>27735</v>
@@ -33684,7 +33684,7 @@
         <v>0.0202254918306102</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>62640</v>
@@ -37343,7 +37343,7 @@
         <v>0.008278113896091423</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>5327</v>
@@ -37361,7 +37361,7 @@
         <v>5585</v>
       </c>
       <c r="K82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83">
@@ -41002,7 +41002,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -44661,7 +44661,7 @@
         <v>0.07789955604883463</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>19648</v>
@@ -48320,7 +48320,7 @@
         <v>0.07481786397065156</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>18745</v>
@@ -51979,7 +51979,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4399,7 +4399,7 @@
         <v>1.71826226409691e-05</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>90046</v>
@@ -4417,7 +4417,7 @@
         <v>11849</v>
       </c>
       <c r="K82" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="83">
@@ -8058,7 +8058,7 @@
         <v>0.03114112002966557</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>51126</v>
@@ -8076,7 +8076,7 @@
         <v>8221</v>
       </c>
       <c r="K82" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="83">
@@ -11717,7 +11717,7 @@
         <v>0.0136672703849116</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>216983</v>
@@ -15376,7 +15376,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -19035,7 +19035,7 @@
         <v>0.0004012911105295298</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>8026</v>
@@ -22694,7 +22694,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>35152</v>
@@ -22712,7 +22712,7 @@
         <v>2006</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -26366,7 +26366,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -30025,7 +30025,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>27735</v>
@@ -30043,7 +30043,7 @@
         <v>5401</v>
       </c>
       <c r="K82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="83">
@@ -33684,7 +33684,7 @@
         <v>0.0202254918306102</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>62640</v>
@@ -33702,7 +33702,7 @@
         <v>5484</v>
       </c>
       <c r="K82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83">
@@ -37343,7 +37343,7 @@
         <v>0.008278113896091423</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>5327</v>
@@ -41002,7 +41002,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -44661,7 +44661,7 @@
         <v>0.07789955604883463</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>19648</v>
@@ -48320,7 +48320,7 @@
         <v>0.07481786397065156</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>18745</v>
@@ -51979,7 +51979,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4399,7 +4399,7 @@
         <v>1.71826226409691e-05</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
         <v>90046</v>
@@ -4417,7 +4417,7 @@
         <v>11849</v>
       </c>
       <c r="K82" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="83">
@@ -8049,16 +8049,16 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>133474</v>
+        <v>133490</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.03114112002966557</v>
+        <v>0.03126472655918049</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
         <v>51126</v>
@@ -8092,7 +8092,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>-0.1262942595561682</v>
+        <v>-0.1263989811970934</v>
       </c>
       <c r="E83" t="n">
         <v>7</v>
@@ -11717,7 +11717,7 @@
         <v>0.0136672703849116</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
         <v>216983</v>
@@ -15376,7 +15376,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -19035,7 +19035,7 @@
         <v>0.0004012911105295298</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
         <v>8026</v>
@@ -22694,7 +22694,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
         <v>35152</v>
@@ -22712,7 +22712,7 @@
         <v>2006</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -26366,7 +26366,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -30025,7 +30025,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
         <v>27735</v>
@@ -30043,7 +30043,7 @@
         <v>5401</v>
       </c>
       <c r="K82" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="83">
@@ -33684,7 +33684,7 @@
         <v>0.0202254918306102</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
         <v>62640</v>
@@ -37343,7 +37343,7 @@
         <v>0.008278113896091423</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
         <v>5327</v>
@@ -41002,7 +41002,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -44661,7 +44661,7 @@
         <v>0.07789955604883463</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
         <v>19648</v>
@@ -48320,7 +48320,7 @@
         <v>0.07481786397065156</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
         <v>18745</v>
@@ -51979,7 +51979,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4417,7 +4417,7 @@
         <v>11849</v>
       </c>
       <c r="K82" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="83">
@@ -11735,7 +11735,7 @@
         <v>30871</v>
       </c>
       <c r="K82" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="83">
@@ -30043,7 +30043,7 @@
         <v>5401</v>
       </c>
       <c r="K82" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4399,7 +4399,7 @@
         <v>1.71826226409691e-05</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F82" t="n">
         <v>90046</v>
@@ -8049,16 +8049,16 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>133490</v>
+        <v>133719</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.03126472655918049</v>
+        <v>0.03303384501286281</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F82" t="n">
         <v>51126</v>
@@ -8092,7 +8092,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>-0.1263989811970934</v>
+        <v>-0.1278950635287431</v>
       </c>
       <c r="E83" t="n">
         <v>7</v>
@@ -11717,7 +11717,7 @@
         <v>0.0136672703849116</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F82" t="n">
         <v>216983</v>
@@ -15376,7 +15376,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -19035,7 +19035,7 @@
         <v>0.0004012911105295298</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F82" t="n">
         <v>8026</v>
@@ -22694,7 +22694,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F82" t="n">
         <v>35152</v>
@@ -26366,7 +26366,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -30025,7 +30025,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F82" t="n">
         <v>27735</v>
@@ -33684,7 +33684,7 @@
         <v>0.0202254918306102</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F82" t="n">
         <v>62640</v>
@@ -37343,7 +37343,7 @@
         <v>0.008278113896091423</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F82" t="n">
         <v>5327</v>
@@ -41002,7 +41002,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -44661,7 +44661,7 @@
         <v>0.07789955604883463</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F82" t="n">
         <v>19648</v>
@@ -48320,7 +48320,7 @@
         <v>0.07481786397065156</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F82" t="n">
         <v>18745</v>
@@ -51979,7 +51979,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4399,7 +4399,7 @@
         <v>1.71826226409691e-05</v>
       </c>
       <c r="E82" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F82" t="n">
         <v>90046</v>
@@ -8058,7 +8058,7 @@
         <v>0.03303384501286281</v>
       </c>
       <c r="E82" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F82" t="n">
         <v>51126</v>
@@ -11717,7 +11717,7 @@
         <v>0.0136672703849116</v>
       </c>
       <c r="E82" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F82" t="n">
         <v>216983</v>
@@ -15376,7 +15376,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -19035,7 +19035,7 @@
         <v>0.0004012911105295298</v>
       </c>
       <c r="E82" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F82" t="n">
         <v>8026</v>
@@ -22694,7 +22694,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F82" t="n">
         <v>35152</v>
@@ -26366,7 +26366,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -30025,7 +30025,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E82" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F82" t="n">
         <v>27735</v>
@@ -33684,7 +33684,7 @@
         <v>0.0202254918306102</v>
       </c>
       <c r="E82" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F82" t="n">
         <v>62640</v>
@@ -37343,7 +37343,7 @@
         <v>0.008278113896091423</v>
       </c>
       <c r="E82" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F82" t="n">
         <v>5327</v>
@@ -41002,7 +41002,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E82" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -44661,7 +44661,7 @@
         <v>0.07789955604883463</v>
       </c>
       <c r="E82" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F82" t="n">
         <v>19648</v>
@@ -48320,7 +48320,7 @@
         <v>0.07481786397065156</v>
       </c>
       <c r="E82" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F82" t="n">
         <v>18745</v>
@@ -51979,7 +51979,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4399,7 +4399,7 @@
         <v>1.71826226409691e-05</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F82" t="n">
         <v>90046</v>
@@ -8058,7 +8058,7 @@
         <v>0.03303384501286281</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F82" t="n">
         <v>51126</v>
@@ -11717,7 +11717,7 @@
         <v>0.0136672703849116</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F82" t="n">
         <v>216983</v>
@@ -15376,7 +15376,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -19035,7 +19035,7 @@
         <v>0.0004012911105295298</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F82" t="n">
         <v>8026</v>
@@ -22694,7 +22694,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F82" t="n">
         <v>35152</v>
@@ -26366,7 +26366,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -30025,7 +30025,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F82" t="n">
         <v>27735</v>
@@ -33675,16 +33675,16 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>97909</v>
+        <v>98014</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.0202254918306102</v>
+        <v>0.02131960653551184</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F82" t="n">
         <v>62640</v>
@@ -33718,7 +33718,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>-0.06956459569600343</v>
+        <v>-0.07056134837880303</v>
       </c>
       <c r="E83" t="n">
         <v>7</v>
@@ -37343,7 +37343,7 @@
         <v>0.008278113896091423</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F82" t="n">
         <v>5327</v>
@@ -41002,7 +41002,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -44652,16 +44652,16 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>15539</v>
+        <v>15290</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.07789955604883463</v>
+        <v>0.06062708102108768</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F82" t="n">
         <v>19648</v>
@@ -44695,7 +44695,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>-0.1222729905399318</v>
+        <v>-0.1079790712884238</v>
       </c>
       <c r="E83" t="n">
         <v>7</v>
@@ -48311,16 +48311,16 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>62405</v>
+        <v>62521</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.07481786397065156</v>
+        <v>0.07681576273229879</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F82" t="n">
         <v>18745</v>
@@ -48354,7 +48354,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>-0.07501001522313917</v>
+        <v>-0.07672621999008333</v>
       </c>
       <c r="E83" t="n">
         <v>7</v>
@@ -51979,7 +51979,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4399,7 +4399,7 @@
         <v>1.71826226409691e-05</v>
       </c>
       <c r="E82" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F82" t="n">
         <v>90046</v>
@@ -8058,7 +8058,7 @@
         <v>0.03303384501286281</v>
       </c>
       <c r="E82" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F82" t="n">
         <v>51126</v>
@@ -11717,7 +11717,7 @@
         <v>0.0136672703849116</v>
       </c>
       <c r="E82" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F82" t="n">
         <v>216983</v>
@@ -15376,7 +15376,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -19035,7 +19035,7 @@
         <v>0.0004012911105295298</v>
       </c>
       <c r="E82" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F82" t="n">
         <v>8026</v>
@@ -22694,7 +22694,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F82" t="n">
         <v>35152</v>
@@ -26366,7 +26366,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -30025,7 +30025,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E82" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F82" t="n">
         <v>27735</v>
@@ -33684,7 +33684,7 @@
         <v>0.02131960653551184</v>
       </c>
       <c r="E82" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F82" t="n">
         <v>62640</v>
@@ -37343,7 +37343,7 @@
         <v>0.008278113896091423</v>
       </c>
       <c r="E82" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F82" t="n">
         <v>5327</v>
@@ -41002,7 +41002,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E82" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -44661,7 +44661,7 @@
         <v>0.06062708102108768</v>
       </c>
       <c r="E82" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F82" t="n">
         <v>19648</v>
@@ -48320,7 +48320,7 @@
         <v>0.07681576273229879</v>
       </c>
       <c r="E82" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F82" t="n">
         <v>18745</v>
@@ -51979,7 +51979,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -4399,7 +4399,7 @@
         <v>1.71826226409691e-05</v>
       </c>
       <c r="E82" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F82" t="n">
         <v>90046</v>
@@ -8058,7 +8058,7 @@
         <v>0.03303384501286281</v>
       </c>
       <c r="E82" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F82" t="n">
         <v>51126</v>
@@ -11717,7 +11717,7 @@
         <v>0.0136672703849116</v>
       </c>
       <c r="E82" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F82" t="n">
         <v>216983</v>
@@ -15376,7 +15376,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -19035,7 +19035,7 @@
         <v>0.0004012911105295298</v>
       </c>
       <c r="E82" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F82" t="n">
         <v>8026</v>
@@ -22694,7 +22694,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F82" t="n">
         <v>35152</v>
@@ -26366,7 +26366,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -30025,7 +30025,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E82" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F82" t="n">
         <v>27735</v>
@@ -33684,7 +33684,7 @@
         <v>0.02131960653551184</v>
       </c>
       <c r="E82" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F82" t="n">
         <v>62640</v>
@@ -37343,7 +37343,7 @@
         <v>0.008278113896091423</v>
       </c>
       <c r="E82" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F82" t="n">
         <v>5327</v>
@@ -41002,7 +41002,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E82" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -44661,7 +44661,7 @@
         <v>0.06062708102108768</v>
       </c>
       <c r="E82" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F82" t="n">
         <v>19648</v>
@@ -48320,7 +48320,7 @@
         <v>0.07681576273229879</v>
       </c>
       <c r="E82" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F82" t="n">
         <v>18745</v>
@@ -51979,7 +51979,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
